--- a/Data Files/MANTIS_Mission_Config_v2.xlsx
+++ b/Data Files/MANTIS_Mission_Config_v2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebastianescobar/Desktop/CubeSatMissionPlanner/Data Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebastianescobar/Desktop/CubeSatMissionPlanner-1/Data Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BF5437-0C3D-E54A-BD81-F3661B561C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09744BAE-204C-B64C-BB93-13DA765C1459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="840" windowWidth="21760" windowHeight="14380" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8360" yWindow="3280" windowWidth="21760" windowHeight="14380" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlanPropagation_Info" sheetId="1" r:id="rId1"/>
@@ -458,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -472,24 +472,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -499,21 +484,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="11" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -521,13 +494,39 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -973,10 +972,10 @@
         <v>8</v>
       </c>
       <c r="D2" s="5">
-        <v>45915.020833333336</v>
+        <v>45748.020833333336</v>
       </c>
       <c r="E2" s="5">
-        <v>45916</v>
+        <v>45751</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -995,3137 +994,3137 @@
   <cols>
     <col min="1" max="1" width="20" style="6" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="11" style="7" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" style="7" customWidth="1"/>
-    <col min="5" max="5" width="10.5" style="8" customWidth="1"/>
-    <col min="6" max="6" width="10.5" style="7" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="8" customWidth="1"/>
-    <col min="9" max="9" width="15.5" style="9" customWidth="1"/>
+    <col min="3" max="3" width="11" style="27" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" style="27" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="28" customWidth="1"/>
+    <col min="6" max="6" width="10.5" style="27" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="27" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="28" customWidth="1"/>
+    <col min="9" max="9" width="15.5" style="6" customWidth="1"/>
     <col min="10" max="10" width="39.1640625" style="6" customWidth="1"/>
     <col min="11" max="11" width="13.6640625" style="6" customWidth="1"/>
-    <col min="12" max="12" width="16.83203125" customWidth="1"/>
-    <col min="13" max="13" width="21.33203125" style="9" customWidth="1"/>
-    <col min="14" max="14" width="21" style="9" customWidth="1"/>
-    <col min="15" max="15" width="24.1640625" style="9" customWidth="1"/>
-    <col min="16" max="1024" width="8.83203125" style="9"/>
+    <col min="12" max="12" width="16.83203125" style="26" customWidth="1"/>
+    <col min="13" max="13" width="21.33203125" style="6" customWidth="1"/>
+    <col min="14" max="14" width="21" style="6" customWidth="1"/>
+    <col min="15" max="15" width="24.1640625" style="6" customWidth="1"/>
+    <col min="16" max="1024" width="8.83203125" style="6"/>
+    <col min="1025" max="16384" width="8.83203125" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:15" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="24">
         <v>10</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="24">
         <v>56</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="25">
         <v>32.393885826175598</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="24">
         <v>7</v>
       </c>
-      <c r="G2" s="19">
+      <c r="G2" s="24">
         <v>1</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2" s="25">
         <v>4.63830791976548</v>
       </c>
-      <c r="I2" s="18">
-        <v>0</v>
-      </c>
-      <c r="J2" s="17" t="s">
+      <c r="I2" s="12">
+        <v>0</v>
+      </c>
+      <c r="J2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="17">
+      <c r="K2" s="12">
         <v>1</v>
       </c>
-      <c r="L2" s="21" t="str">
+      <c r="L2" s="12" t="str">
         <f>LOOKUP(J2,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M2" s="21">
+      <c r="M2" s="12">
         <f>LOOKUP(J2,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N2" s="21">
+      <c r="N2" s="12">
         <f>LOOKUP(J2,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O2" s="21">
+      <c r="O2" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="24">
         <v>18</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="24">
         <v>49</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="25">
         <v>49.210696013120099</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="24">
         <v>-23</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="24">
         <v>50</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3" s="25">
         <v>7.3612248625721604</v>
       </c>
-      <c r="I3" s="18">
-        <v>0</v>
-      </c>
-      <c r="J3" s="17" t="s">
+      <c r="I3" s="12">
+        <v>0</v>
+      </c>
+      <c r="J3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="12">
         <v>1</v>
       </c>
-      <c r="L3" s="21" t="str">
+      <c r="L3" s="12" t="str">
         <f>LOOKUP(J3,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="12">
         <f>LOOKUP(J3,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="12">
         <f>LOOKUP(J3,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="24">
         <v>23</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="24">
         <v>5</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="25">
         <v>51.434423615327802</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="24">
         <v>-35</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="24">
         <v>50</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="25">
         <v>59.856355732299001</v>
       </c>
-      <c r="I4" s="18">
-        <v>0</v>
-      </c>
-      <c r="J4" s="17" t="s">
+      <c r="I4" s="12">
+        <v>0</v>
+      </c>
+      <c r="J4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="17">
+      <c r="K4" s="12">
         <v>1</v>
       </c>
-      <c r="L4" s="21" t="str">
+      <c r="L4" s="12" t="str">
         <f>LOOKUP(J4,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M4" s="21">
+      <c r="M4" s="12">
         <f>LOOKUP(J4,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N4" s="21">
+      <c r="N4" s="12">
         <f>LOOKUP(J4,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O4" s="21">
+      <c r="O4" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="24">
         <v>1</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="24">
         <v>12</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="25">
         <v>31.981020890259401</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="24">
         <v>-16</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="24">
         <v>59</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="25">
         <v>46.157540925243801</v>
       </c>
-      <c r="I5" s="18">
-        <v>0</v>
-      </c>
-      <c r="J5" s="17" t="s">
+      <c r="I5" s="12">
+        <v>0</v>
+      </c>
+      <c r="J5" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="12">
         <v>1</v>
       </c>
-      <c r="L5" s="21" t="str">
+      <c r="L5" s="12" t="str">
         <f>LOOKUP(J5,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M5" s="21">
+      <c r="M5" s="12">
         <f>LOOKUP(J5,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N5" s="21">
+      <c r="N5" s="12">
         <f>LOOKUP(J5,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O5" s="21">
+      <c r="O5" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="24">
         <v>21</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="24">
         <v>17</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="25">
         <v>15.078769011376201</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="24">
         <v>-38</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="24">
         <v>51</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="25">
         <v>51.824437783408797</v>
       </c>
-      <c r="I6" s="18">
-        <v>0</v>
-      </c>
-      <c r="J6" s="17" t="s">
+      <c r="I6" s="12">
+        <v>0</v>
+      </c>
+      <c r="J6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="12">
         <v>1</v>
       </c>
-      <c r="L6" s="21" t="str">
+      <c r="L6" s="12" t="str">
         <f>LOOKUP(J6,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M6" s="21">
+      <c r="M6" s="12">
         <f>LOOKUP(J6,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N6" s="21">
+      <c r="N6" s="12">
         <f>LOOKUP(J6,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O6" s="21">
+      <c r="O6" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="24">
         <v>6</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="24">
         <v>29</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="25">
         <v>23.699547247678399</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="24">
         <v>-2</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="24">
         <v>48</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="25">
         <v>38.3026274148</v>
       </c>
-      <c r="I7" s="18">
-        <v>0</v>
-      </c>
-      <c r="J7" s="17" t="s">
+      <c r="I7" s="12">
+        <v>0</v>
+      </c>
+      <c r="J7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="12">
         <v>1</v>
       </c>
-      <c r="L7" s="21" t="str">
+      <c r="L7" s="12" t="str">
         <f>LOOKUP(J7,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M7" s="21">
+      <c r="M7" s="12">
         <f>LOOKUP(J7,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N7" s="21">
+      <c r="N7" s="12">
         <f>LOOKUP(J7,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O7" s="21">
+      <c r="O7" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="24">
         <v>5</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="24">
         <v>31</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="25">
         <v>27.547598227848098</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="24">
         <v>-3</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="24">
         <v>40</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="25">
         <v>51.948487452882098</v>
       </c>
-      <c r="I8" s="18">
-        <v>0</v>
-      </c>
-      <c r="J8" s="17" t="s">
+      <c r="I8" s="12">
+        <v>0</v>
+      </c>
+      <c r="J8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="12">
         <v>1</v>
       </c>
-      <c r="L8" s="21" t="str">
+      <c r="L8" s="12" t="str">
         <f>LOOKUP(J8,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M8" s="21">
+      <c r="M8" s="12">
         <f>LOOKUP(J8,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N8" s="21">
+      <c r="N8" s="12">
         <f>LOOKUP(J8,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O8" s="21">
+      <c r="O8" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="24">
         <v>4</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="24">
         <v>59</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="25">
         <v>34.876047408282197</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="24">
         <v>1</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="24">
         <v>46</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="25">
         <v>59.151394152070097</v>
       </c>
-      <c r="I9" s="21">
-        <v>0</v>
-      </c>
-      <c r="J9" s="17" t="s">
+      <c r="I9" s="12">
+        <v>0</v>
+      </c>
+      <c r="J9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="12">
         <v>1</v>
       </c>
-      <c r="L9" s="21" t="str">
+      <c r="L9" s="12" t="str">
         <f>LOOKUP(J9,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M9" s="21">
+      <c r="M9" s="12">
         <f>LOOKUP(J9,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N9" s="21">
+      <c r="N9" s="12">
         <f>LOOKUP(J9,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O9" s="21">
+      <c r="O9" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="24">
         <v>10</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="24">
         <v>11</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="25">
         <v>19.9029499757054</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="24">
         <v>49</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="24">
         <v>27</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="25">
         <v>7.1600295618213803</v>
       </c>
-      <c r="I10" s="18">
-        <v>0</v>
-      </c>
-      <c r="J10" s="17" t="s">
+      <c r="I10" s="12">
+        <v>0</v>
+      </c>
+      <c r="J10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="12">
         <v>1</v>
       </c>
-      <c r="L10" s="21" t="str">
+      <c r="L10" s="12" t="str">
         <f>LOOKUP(J10,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M10" s="21">
+      <c r="M10" s="12">
         <f>LOOKUP(J10,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N10" s="21">
+      <c r="N10" s="12">
         <f>LOOKUP(J10,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O10" s="21">
+      <c r="O10" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="24">
         <v>3</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="24">
         <v>32</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="25">
         <v>54.790419642112802</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="24">
         <v>-9</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="24">
         <v>27</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="25">
         <v>29.405578652357502</v>
       </c>
-      <c r="I11" s="18">
-        <v>0</v>
-      </c>
-      <c r="J11" s="17" t="s">
+      <c r="I11" s="12">
+        <v>0</v>
+      </c>
+      <c r="J11" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="12">
         <v>1</v>
       </c>
-      <c r="L11" s="21" t="str">
+      <c r="L11" s="12" t="str">
         <f>LOOKUP(J11,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M11" s="21">
+      <c r="M11" s="12">
         <f>LOOKUP(J11,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N11" s="21">
+      <c r="N11" s="12">
         <f>LOOKUP(J11,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O11" s="21">
+      <c r="O11" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="24">
         <v>22</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="24">
         <v>56</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="25">
         <v>24.465936417414898</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="24">
         <v>-31</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="24">
         <v>33</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="25">
         <v>58.568263683806997</v>
       </c>
-      <c r="I12" s="18">
-        <v>0</v>
-      </c>
-      <c r="J12" s="17" t="s">
+      <c r="I12" s="12">
+        <v>0</v>
+      </c>
+      <c r="J12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K12" s="17">
+      <c r="K12" s="12">
         <v>1</v>
       </c>
-      <c r="L12" s="21" t="str">
+      <c r="L12" s="12" t="str">
         <f>LOOKUP(J12,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M12" s="21">
+      <c r="M12" s="12">
         <f>LOOKUP(J12,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N12" s="21">
+      <c r="N12" s="12">
         <f>LOOKUP(J12,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O12" s="21">
+      <c r="O12" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="24">
         <v>4</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="24">
         <v>54</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="25">
         <v>32.059326728227497</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="24">
         <v>-11</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="24">
         <v>54</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="25">
         <v>49.132256646964699</v>
       </c>
-      <c r="I13" s="18">
-        <v>0</v>
-      </c>
-      <c r="J13" s="17" t="s">
+      <c r="I13" s="12">
+        <v>0</v>
+      </c>
+      <c r="J13" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="12">
         <v>1</v>
       </c>
-      <c r="L13" s="21" t="str">
+      <c r="L13" s="12" t="str">
         <f>LOOKUP(J13,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M13" s="21">
+      <c r="M13" s="12">
         <f>LOOKUP(J13,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N13" s="21">
+      <c r="N13" s="12">
         <f>LOOKUP(J13,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O13" s="21">
+      <c r="O13" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="24">
         <v>8</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="24">
         <v>39</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="25">
         <v>11.635719032826399</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="24">
         <v>65</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="24">
         <v>1</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="25">
         <v>16.6691960703326</v>
       </c>
-      <c r="I14" s="18">
-        <v>0</v>
-      </c>
-      <c r="J14" s="17" t="s">
+      <c r="I14" s="12">
+        <v>0</v>
+      </c>
+      <c r="J14" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K14" s="17">
+      <c r="K14" s="12">
         <v>1</v>
       </c>
-      <c r="L14" s="21" t="str">
+      <c r="L14" s="12" t="str">
         <f>LOOKUP(J14,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M14" s="21">
+      <c r="M14" s="12">
         <f>LOOKUP(J14,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N14" s="21">
+      <c r="N14" s="12">
         <f>LOOKUP(J14,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O14" s="21">
+      <c r="O14" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="24">
         <v>4</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="24">
         <v>49</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="25">
         <v>50.909765085849003</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="24">
         <v>6</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="24">
         <v>57</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="25">
         <v>40.7916307348722</v>
       </c>
-      <c r="I15" s="18">
-        <v>0</v>
-      </c>
-      <c r="J15" s="17" t="s">
+      <c r="I15" s="12">
+        <v>0</v>
+      </c>
+      <c r="J15" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="12">
         <v>1</v>
       </c>
-      <c r="L15" s="21" t="str">
+      <c r="L15" s="12" t="str">
         <f>LOOKUP(J15,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M15" s="21">
+      <c r="M15" s="12">
         <f>LOOKUP(J15,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N15" s="21">
+      <c r="N15" s="12">
         <f>LOOKUP(J15,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O15" s="21">
+      <c r="O15" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="14">
         <v>9</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="14">
         <v>32</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="14">
         <v>49.809547494094197</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="14">
         <v>51</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="14">
         <v>40</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="14">
         <v>29.661747492156099</v>
       </c>
-      <c r="I16" s="18">
-        <v>0</v>
-      </c>
-      <c r="J16" s="17" t="s">
+      <c r="I16" s="12">
+        <v>0</v>
+      </c>
+      <c r="J16" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="12">
         <v>1</v>
       </c>
-      <c r="L16" s="21" t="str">
+      <c r="L16" s="12" t="str">
         <f>LOOKUP(J16,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M16" s="21">
+      <c r="M16" s="12">
         <f>LOOKUP(J16,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N16" s="21">
+      <c r="N16" s="12">
         <f>LOOKUP(J16,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O16" s="21">
+      <c r="O16" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="14">
         <v>13</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="14">
         <v>47</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="14">
         <v>15.2138386806814</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="14">
         <v>17</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="14">
         <v>27</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="14">
         <v>25.825095813872</v>
       </c>
-      <c r="I17" s="18">
-        <v>0</v>
-      </c>
-      <c r="J17" s="17" t="s">
+      <c r="I17" s="12">
+        <v>0</v>
+      </c>
+      <c r="J17" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17" s="12">
         <v>1</v>
       </c>
-      <c r="L17" s="21" t="str">
+      <c r="L17" s="12" t="str">
         <f>LOOKUP(J17,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M17" s="21">
+      <c r="M17" s="12">
         <f>LOOKUP(J17,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N17" s="21">
+      <c r="N17" s="12">
         <f>LOOKUP(J17,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O17" s="21">
+      <c r="O17" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="14">
         <v>4</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="14">
         <v>36.904305187416099</v>
       </c>
-      <c r="F18" s="23">
-        <v>0</v>
-      </c>
-      <c r="G18" s="23">
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
         <v>16</v>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="14">
         <v>12.1454138384949</v>
       </c>
-      <c r="I18" s="18">
-        <v>0</v>
-      </c>
-      <c r="J18" s="17" t="s">
+      <c r="I18" s="12">
+        <v>0</v>
+      </c>
+      <c r="J18" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K18" s="17">
+      <c r="K18" s="12">
         <v>1</v>
       </c>
-      <c r="L18" s="21" t="str">
+      <c r="L18" s="12" t="str">
         <f>LOOKUP(J18,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M18" s="21">
+      <c r="M18" s="12">
         <f>LOOKUP(J18,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N18" s="21">
+      <c r="N18" s="12">
         <f>LOOKUP(J18,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O18" s="21">
+      <c r="O18" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="14">
         <v>22</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="14">
         <v>46</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="14">
         <v>49.283184772419901</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="14">
         <v>44</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="14">
         <v>19</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="14">
         <v>59.560595522098097</v>
       </c>
-      <c r="I19" s="18">
-        <v>0</v>
-      </c>
-      <c r="J19" s="17" t="s">
+      <c r="I19" s="12">
+        <v>0</v>
+      </c>
+      <c r="J19" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="12">
         <v>1</v>
       </c>
-      <c r="L19" s="21" t="str">
+      <c r="L19" s="12" t="str">
         <f>LOOKUP(J19,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M19" s="21">
+      <c r="M19" s="12">
         <f>LOOKUP(J19,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N19" s="21">
+      <c r="N19" s="12">
         <f>LOOKUP(J19,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O19" s="21">
+      <c r="O19" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="14">
         <v>44</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="14">
         <v>4.3800940711717802</v>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="14">
         <v>-15</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="14">
         <v>56</v>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="14">
         <v>32.357259787263501</v>
       </c>
-      <c r="I20" s="18">
-        <v>0</v>
-      </c>
-      <c r="J20" s="17" t="s">
+      <c r="I20" s="12">
+        <v>0</v>
+      </c>
+      <c r="J20" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="17">
+      <c r="K20" s="12">
         <v>1</v>
       </c>
-      <c r="L20" s="21" t="str">
+      <c r="L20" s="12" t="str">
         <f>LOOKUP(J20,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M20" s="21">
+      <c r="M20" s="12">
         <f>LOOKUP(J20,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N20" s="21">
+      <c r="N20" s="12">
         <f>LOOKUP(J20,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O20" s="21">
+      <c r="O20" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="14">
         <v>7</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="14">
         <v>39</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="14">
         <v>17.7574773317458</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="14">
         <v>5</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="14">
         <v>14</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="14">
         <v>14.713134425050599</v>
       </c>
-      <c r="I21" s="18">
-        <v>0</v>
-      </c>
-      <c r="J21" s="17" t="s">
+      <c r="I21" s="12">
+        <v>0</v>
+      </c>
+      <c r="J21" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="12">
         <v>1</v>
       </c>
-      <c r="L21" s="21" t="str">
+      <c r="L21" s="12" t="str">
         <f>LOOKUP(J21,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M21" s="21">
+      <c r="M21" s="12">
         <f>LOOKUP(J21,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N21" s="21">
+      <c r="N21" s="12">
         <f>LOOKUP(J21,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O21" s="21">
+      <c r="O21" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="14">
         <v>20</v>
       </c>
-      <c r="D22" s="23">
-        <v>0</v>
-      </c>
-      <c r="E22" s="23">
+      <c r="D22" s="14">
+        <v>0</v>
+      </c>
+      <c r="E22" s="14">
         <v>43.712899999999998</v>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="14">
         <v>22</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="14">
         <v>42</v>
       </c>
-      <c r="H22" s="23">
+      <c r="H22" s="14">
         <v>39.073</v>
       </c>
-      <c r="I22" s="18">
-        <v>0</v>
-      </c>
-      <c r="J22" s="22" t="s">
+      <c r="I22" s="12">
+        <v>0</v>
+      </c>
+      <c r="J22" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K22" s="17">
+      <c r="K22" s="12">
         <v>1</v>
       </c>
-      <c r="L22" s="21" t="str">
+      <c r="L22" s="12" t="str">
         <f>LOOKUP(J22,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M22" s="21">
+      <c r="M22" s="12">
         <f>LOOKUP(J22,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N22" s="21">
+      <c r="N22" s="12">
         <f>LOOKUP(J22,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O22" s="21">
+      <c r="O22" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C23" s="23">
+      <c r="C23" s="14">
         <v>8</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="14">
         <v>52</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="14">
         <v>35.811100000000003</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="14">
         <v>28</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="14">
         <v>19</v>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="14">
         <v>50.954000000000001</v>
       </c>
-      <c r="I23" s="18">
-        <v>0</v>
-      </c>
-      <c r="J23" s="22" t="s">
+      <c r="I23" s="12">
+        <v>0</v>
+      </c>
+      <c r="J23" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="12">
         <v>1</v>
       </c>
-      <c r="L23" s="21" t="str">
+      <c r="L23" s="12" t="str">
         <f>LOOKUP(J23,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M23" s="21">
+      <c r="M23" s="12">
         <f>LOOKUP(J23,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N23" s="21">
+      <c r="N23" s="12">
         <f>LOOKUP(J23,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O23" s="21">
+      <c r="O23" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="23">
+      <c r="C24" s="14">
         <v>9</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="14">
         <v>36</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="14">
         <v>1.6372</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="14">
         <v>-21</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="14">
         <v>39</v>
       </c>
-      <c r="H24" s="23">
+      <c r="H24" s="14">
         <v>38.877000000000002</v>
       </c>
-      <c r="I24" s="18">
-        <v>0</v>
-      </c>
-      <c r="J24" s="22" t="s">
+      <c r="I24" s="12">
+        <v>0</v>
+      </c>
+      <c r="J24" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K24" s="17">
+      <c r="K24" s="12">
         <v>1</v>
       </c>
-      <c r="L24" s="21" t="str">
+      <c r="L24" s="12" t="str">
         <f>LOOKUP(J24,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M24" s="21">
+      <c r="M24" s="12">
         <f>LOOKUP(J24,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N24" s="21">
+      <c r="N24" s="12">
         <f>LOOKUP(J24,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O24" s="21">
+      <c r="O24" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="23">
+      <c r="C25" s="14">
         <v>8</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="14">
         <v>18</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="14">
         <v>7.6214000000000004</v>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="14">
         <v>-68</v>
       </c>
-      <c r="G25" s="23">
+      <c r="G25" s="14">
         <v>18</v>
       </c>
-      <c r="H25" s="23">
+      <c r="H25" s="14">
         <v>46.805</v>
       </c>
-      <c r="I25" s="18">
-        <v>0</v>
-      </c>
-      <c r="J25" s="22" t="s">
+      <c r="I25" s="12">
+        <v>0</v>
+      </c>
+      <c r="J25" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K25" s="17">
+      <c r="K25" s="12">
         <v>1</v>
       </c>
-      <c r="L25" s="21" t="str">
+      <c r="L25" s="12" t="str">
         <f>LOOKUP(J25,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M25" s="21">
+      <c r="M25" s="12">
         <f>LOOKUP(J25,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N25" s="21">
+      <c r="N25" s="12">
         <f>LOOKUP(J25,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O25" s="21">
+      <c r="O25" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="23">
+      <c r="C26" s="14">
         <v>15</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="14">
         <v>9</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="14">
         <v>4.8933</v>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="14">
         <v>-42</v>
       </c>
-      <c r="G26" s="23">
+      <c r="G26" s="14">
         <v>42</v>
       </c>
-      <c r="H26" s="23">
+      <c r="H26" s="14">
         <v>17.789000000000001</v>
       </c>
-      <c r="I26" s="18">
-        <v>0</v>
-      </c>
-      <c r="J26" s="22" t="s">
+      <c r="I26" s="12">
+        <v>0</v>
+      </c>
+      <c r="J26" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K26" s="17">
+      <c r="K26" s="12">
         <v>1</v>
       </c>
-      <c r="L26" s="21" t="str">
+      <c r="L26" s="12" t="str">
         <f>LOOKUP(J26,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M26" s="21">
+      <c r="M26" s="12">
         <f>LOOKUP(J26,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N26" s="21">
+      <c r="N26" s="12">
         <f>LOOKUP(J26,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O26" s="21">
+      <c r="O26" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C27" s="23">
+      <c r="C27" s="14">
         <v>4</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="14">
         <v>5</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="14">
         <v>19.590900000000001</v>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="14">
         <v>20</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="14">
         <v>9</v>
       </c>
-      <c r="H27" s="23">
+      <c r="H27" s="14">
         <v>25.562999999999999</v>
       </c>
-      <c r="I27" s="18">
-        <v>0</v>
-      </c>
-      <c r="J27" s="22" t="s">
+      <c r="I27" s="12">
+        <v>0</v>
+      </c>
+      <c r="J27" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K27" s="17">
+      <c r="K27" s="12">
         <v>1</v>
       </c>
-      <c r="L27" s="21" t="str">
+      <c r="L27" s="12" t="str">
         <f>LOOKUP(J27,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M27" s="21">
+      <c r="M27" s="12">
         <f>LOOKUP(J27,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N27" s="21">
+      <c r="N27" s="12">
         <f>LOOKUP(J27,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O27" s="21">
+      <c r="O27" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C28" s="23">
+      <c r="C28" s="14">
         <v>22</v>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="14">
         <v>3</v>
       </c>
-      <c r="E28" s="23">
+      <c r="E28" s="14">
         <v>10.7727</v>
       </c>
-      <c r="F28" s="23">
+      <c r="F28" s="14">
         <v>18</v>
       </c>
-      <c r="G28" s="23">
+      <c r="G28" s="14">
         <v>53</v>
       </c>
-      <c r="H28" s="23">
+      <c r="H28" s="14">
         <v>3.5489999999999999</v>
       </c>
-      <c r="I28" s="18">
-        <v>0</v>
-      </c>
-      <c r="J28" s="22" t="s">
+      <c r="I28" s="12">
+        <v>0</v>
+      </c>
+      <c r="J28" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K28" s="17">
+      <c r="K28" s="12">
         <v>1</v>
       </c>
-      <c r="L28" s="21" t="str">
+      <c r="L28" s="12" t="str">
         <f>LOOKUP(J28,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M28" s="21">
+      <c r="M28" s="12">
         <f>LOOKUP(J28,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N28" s="21">
+      <c r="N28" s="12">
         <f>LOOKUP(J28,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O28" s="21">
+      <c r="O28" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C29" s="23">
+      <c r="C29" s="14">
         <v>3</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="14">
         <v>51.393599999999999</v>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="14">
         <v>-16</v>
       </c>
-      <c r="G29" s="23">
+      <c r="G29" s="14">
         <v>35</v>
       </c>
-      <c r="H29" s="23">
+      <c r="H29" s="14">
         <v>36.030999999999999</v>
       </c>
-      <c r="I29" s="18">
-        <v>0</v>
-      </c>
-      <c r="J29" s="22" t="s">
+      <c r="I29" s="12">
+        <v>0</v>
+      </c>
+      <c r="J29" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K29" s="17">
+      <c r="K29" s="12">
         <v>1</v>
       </c>
-      <c r="L29" s="21" t="str">
+      <c r="L29" s="12" t="str">
         <f>LOOKUP(J29,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M29" s="21">
+      <c r="M29" s="12">
         <f>LOOKUP(J29,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N29" s="21">
+      <c r="N29" s="12">
         <f>LOOKUP(J29,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O29" s="21">
+      <c r="O29" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="23">
+      <c r="C30" s="14">
         <v>12</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="14">
         <v>47</v>
       </c>
-      <c r="E30" s="23">
+      <c r="E30" s="14">
         <v>56.624499999999998</v>
       </c>
-      <c r="F30" s="23">
+      <c r="F30" s="14">
         <v>9</v>
       </c>
-      <c r="G30" s="23">
+      <c r="G30" s="14">
         <v>45</v>
       </c>
-      <c r="H30" s="23">
+      <c r="H30" s="14">
         <v>5.0350000000000001</v>
       </c>
-      <c r="I30" s="18">
-        <v>0</v>
-      </c>
-      <c r="J30" s="22" t="s">
+      <c r="I30" s="12">
+        <v>0</v>
+      </c>
+      <c r="J30" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K30" s="17">
+      <c r="K30" s="12">
         <v>1</v>
       </c>
-      <c r="L30" s="21" t="str">
+      <c r="L30" s="12" t="str">
         <f>LOOKUP(J30,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M30" s="21">
+      <c r="M30" s="12">
         <f>LOOKUP(J30,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N30" s="21">
+      <c r="N30" s="12">
         <f>LOOKUP(J30,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O30" s="21">
+      <c r="O30" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C31" s="23">
+      <c r="C31" s="14">
         <v>9</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="14">
         <v>44</v>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="14">
         <v>29.8367</v>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="14">
         <v>-45</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="14">
         <v>46</v>
       </c>
-      <c r="H31" s="23">
+      <c r="H31" s="14">
         <v>35.427</v>
       </c>
-      <c r="I31" s="18">
-        <v>0</v>
-      </c>
-      <c r="J31" s="22" t="s">
+      <c r="I31" s="12">
+        <v>0</v>
+      </c>
+      <c r="J31" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K31" s="17">
+      <c r="K31" s="12">
         <v>1</v>
       </c>
-      <c r="L31" s="21" t="str">
+      <c r="L31" s="12" t="str">
         <f>LOOKUP(J31,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M31" s="21">
+      <c r="M31" s="12">
         <f>LOOKUP(J31,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N31" s="21">
+      <c r="N31" s="12">
         <f>LOOKUP(J31,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O31" s="21">
+      <c r="O31" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="23">
+      <c r="C32" s="14">
         <v>9</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="14">
         <v>21</v>
       </c>
-      <c r="E32" s="23">
+      <c r="E32" s="14">
         <v>37.601500000000001</v>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="14">
         <v>-60</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="14">
         <v>16</v>
       </c>
-      <c r="H32" s="23">
+      <c r="H32" s="14">
         <v>55.03</v>
       </c>
-      <c r="I32" s="18">
-        <v>0</v>
-      </c>
-      <c r="J32" s="22" t="s">
+      <c r="I32" s="12">
+        <v>0</v>
+      </c>
+      <c r="J32" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K32" s="17">
+      <c r="K32" s="12">
         <v>1</v>
       </c>
-      <c r="L32" s="21" t="str">
+      <c r="L32" s="12" t="str">
         <f>LOOKUP(J32,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M32" s="21">
+      <c r="M32" s="12">
         <f>LOOKUP(J32,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N32" s="21">
+      <c r="N32" s="12">
         <f>LOOKUP(J32,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O32" s="21">
+      <c r="O32" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="23">
+      <c r="C33" s="14">
         <v>19</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="14">
         <v>20</v>
       </c>
-      <c r="E33" s="23">
+      <c r="E33" s="14">
         <v>54.376100000000001</v>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="14">
         <v>-82</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="14">
         <v>33</v>
       </c>
-      <c r="H33" s="23">
+      <c r="H33" s="14">
         <v>16.167000000000002</v>
       </c>
-      <c r="I33" s="18">
-        <v>0</v>
-      </c>
-      <c r="J33" s="22" t="s">
+      <c r="I33" s="12">
+        <v>0</v>
+      </c>
+      <c r="J33" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K33" s="17">
+      <c r="K33" s="12">
         <v>1</v>
       </c>
-      <c r="L33" s="21" t="str">
+      <c r="L33" s="12" t="str">
         <f>LOOKUP(J33,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M33" s="21">
+      <c r="M33" s="12">
         <f>LOOKUP(J33,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N33" s="21">
+      <c r="N33" s="12">
         <f>LOOKUP(J33,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O33" s="21">
+      <c r="O33" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="23">
-        <v>0</v>
-      </c>
-      <c r="D34" s="23">
+      <c r="C34" s="14">
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
         <v>19</v>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="14">
         <v>5.5622999999999996</v>
       </c>
-      <c r="F34" s="23">
+      <c r="F34" s="14">
         <v>-9</v>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="14">
         <v>57</v>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="14">
         <v>53.468000000000004</v>
       </c>
-      <c r="I34" s="18">
-        <v>0</v>
-      </c>
-      <c r="J34" s="22" t="s">
+      <c r="I34" s="12">
+        <v>0</v>
+      </c>
+      <c r="J34" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K34" s="17">
+      <c r="K34" s="12">
         <v>1</v>
       </c>
-      <c r="L34" s="21" t="str">
+      <c r="L34" s="12" t="str">
         <f>LOOKUP(J34,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M34" s="21">
+      <c r="M34" s="12">
         <f>LOOKUP(J34,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N34" s="21">
+      <c r="N34" s="12">
         <f>LOOKUP(J34,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O34" s="21">
+      <c r="O34" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C35" s="23">
+      <c r="C35" s="14">
         <v>11</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="14">
         <v>54</v>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="14">
         <v>18.392099999999999</v>
       </c>
-      <c r="F35" s="23">
+      <c r="F35" s="14">
         <v>-37</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="14">
         <v>33</v>
       </c>
-      <c r="H35" s="23">
+      <c r="H35" s="14">
         <v>9.8369999999999997</v>
       </c>
-      <c r="I35" s="18">
-        <v>0</v>
-      </c>
-      <c r="J35" s="22" t="s">
+      <c r="I35" s="12">
+        <v>0</v>
+      </c>
+      <c r="J35" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K35" s="17">
+      <c r="K35" s="12">
         <v>1</v>
       </c>
-      <c r="L35" s="21" t="str">
+      <c r="L35" s="12" t="str">
         <f>LOOKUP(J35,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M35" s="21">
+      <c r="M35" s="12">
         <f>LOOKUP(J35,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N35" s="21">
+      <c r="N35" s="12">
         <f>LOOKUP(J35,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O35" s="21">
+      <c r="O35" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="23">
+      <c r="C36" s="14">
         <v>15</v>
       </c>
-      <c r="D36" s="23">
-        <v>0</v>
-      </c>
-      <c r="E36" s="23">
+      <c r="D36" s="14">
+        <v>0</v>
+      </c>
+      <c r="E36" s="14">
         <v>19.398299999999999</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="14">
         <v>-24</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="14">
         <v>27</v>
       </c>
-      <c r="H36" s="23">
+      <c r="H36" s="14">
         <v>14.693</v>
       </c>
-      <c r="I36" s="18">
-        <v>0</v>
-      </c>
-      <c r="J36" s="22" t="s">
+      <c r="I36" s="12">
+        <v>0</v>
+      </c>
+      <c r="J36" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K36" s="17">
-        <v>1</v>
-      </c>
-      <c r="L36" s="21" t="str">
+      <c r="K36" s="12">
+        <v>-1</v>
+      </c>
+      <c r="L36" s="12" t="str">
         <f>LOOKUP(J36,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M36" s="21">
-        <f>LOOKUP(J36,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N36" s="21">
+      <c r="M36" s="12">
+        <v>300</v>
+      </c>
+      <c r="N36" s="12">
         <f>LOOKUP(J36,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O36" s="21">
+      <c r="O36" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="23">
+      <c r="C37" s="14">
         <v>2</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="14">
         <v>27</v>
       </c>
-      <c r="E37" s="23">
+      <c r="E37" s="14">
         <v>28.3781</v>
       </c>
-      <c r="F37" s="23">
+      <c r="F37" s="14">
         <v>-27</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="14">
         <v>38</v>
       </c>
-      <c r="H37" s="23">
+      <c r="H37" s="14">
         <v>6.7359999999999998</v>
       </c>
-      <c r="I37" s="18">
-        <v>0</v>
-      </c>
-      <c r="J37" s="22" t="s">
+      <c r="I37" s="12">
+        <v>0</v>
+      </c>
+      <c r="J37" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K37" s="17">
+      <c r="K37" s="12">
         <v>1</v>
       </c>
-      <c r="L37" s="21" t="str">
+      <c r="L37" s="12" t="str">
         <f>LOOKUP(J37,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M37" s="21">
+      <c r="M37" s="12">
         <f>LOOKUP(J37,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N37" s="21">
+      <c r="N37" s="12">
         <f>LOOKUP(J37,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O37" s="21">
+      <c r="O37" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C38" s="23">
+      <c r="C38" s="14">
         <v>9</v>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="14">
         <v>22</v>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="14">
         <v>37.576799999999999</v>
       </c>
-      <c r="F38" s="23">
+      <c r="F38" s="14">
         <v>50</v>
       </c>
-      <c r="G38" s="23">
+      <c r="G38" s="14">
         <v>36</v>
       </c>
-      <c r="H38" s="23">
+      <c r="H38" s="14">
         <v>13.435</v>
       </c>
-      <c r="I38" s="18">
-        <v>0</v>
-      </c>
-      <c r="J38" s="22" t="s">
+      <c r="I38" s="12">
+        <v>0</v>
+      </c>
+      <c r="J38" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K38" s="17">
+      <c r="K38" s="12">
         <v>1</v>
       </c>
-      <c r="L38" s="21" t="str">
+      <c r="L38" s="12" t="str">
         <f>LOOKUP(J38,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M38" s="21">
+      <c r="M38" s="12">
         <f>LOOKUP(J38,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N38" s="21">
+      <c r="N38" s="12">
         <f>LOOKUP(J38,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O38" s="21">
+      <c r="O38" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C39" s="23">
+      <c r="C39" s="14">
         <v>5</v>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="14">
         <v>27</v>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="14">
         <v>24.825800000000001</v>
       </c>
-      <c r="F39" s="23">
+      <c r="F39" s="14">
         <v>-14</v>
       </c>
-      <c r="G39" s="23">
+      <c r="G39" s="14">
         <v>16</v>
       </c>
-      <c r="H39" s="23">
+      <c r="H39" s="14">
         <v>37.045999999999999</v>
       </c>
-      <c r="I39" s="18">
-        <v>0</v>
-      </c>
-      <c r="J39" s="22" t="s">
+      <c r="I39" s="12">
+        <v>0</v>
+      </c>
+      <c r="J39" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K39" s="17">
+      <c r="K39" s="12">
         <v>1</v>
       </c>
-      <c r="L39" s="21" t="str">
+      <c r="L39" s="12" t="str">
         <f>LOOKUP(J39,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M39" s="21">
+      <c r="M39" s="12">
         <f>LOOKUP(J39,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N39" s="21">
+      <c r="N39" s="12">
         <f>LOOKUP(J39,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O39" s="21">
+      <c r="O39" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
+      <c r="A40" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C40" s="23">
+      <c r="C40" s="14">
         <v>9</v>
       </c>
-      <c r="D40" s="23">
+      <c r="D40" s="14">
         <v>39</v>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="14">
         <v>30.086099999999998</v>
       </c>
-      <c r="F40" s="23">
+      <c r="F40" s="14">
         <v>-20</v>
       </c>
-      <c r="G40" s="23">
+      <c r="G40" s="14">
         <v>58</v>
       </c>
-      <c r="H40" s="23">
+      <c r="H40" s="14">
         <v>56.881</v>
       </c>
-      <c r="I40" s="18">
-        <v>0</v>
-      </c>
-      <c r="J40" s="22" t="s">
+      <c r="I40" s="12">
+        <v>0</v>
+      </c>
+      <c r="J40" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K40" s="17">
+      <c r="K40" s="12">
         <v>1</v>
       </c>
-      <c r="L40" s="21" t="str">
+      <c r="L40" s="12" t="str">
         <f>LOOKUP(J40,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M40" s="21">
+      <c r="M40" s="12">
         <f>LOOKUP(J40,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N40" s="21">
+      <c r="N40" s="12">
         <f>LOOKUP(J40,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O40" s="21">
+      <c r="O40" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="22" t="s">
+      <c r="A41" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="23">
+      <c r="C41" s="14">
         <v>7</v>
       </c>
-      <c r="D41" s="23">
+      <c r="D41" s="14">
         <v>10</v>
       </c>
-      <c r="E41" s="23">
+      <c r="E41" s="14">
         <v>24.060400000000001</v>
       </c>
-      <c r="F41" s="23">
+      <c r="F41" s="14">
         <v>-39</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G41" s="14">
         <v>5</v>
       </c>
-      <c r="H41" s="23">
+      <c r="H41" s="14">
         <v>50.570999999999998</v>
       </c>
-      <c r="I41" s="18">
-        <v>0</v>
-      </c>
-      <c r="J41" s="22" t="s">
+      <c r="I41" s="12">
+        <v>0</v>
+      </c>
+      <c r="J41" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K41" s="17">
+      <c r="K41" s="12">
         <v>1</v>
       </c>
-      <c r="L41" s="21" t="str">
+      <c r="L41" s="12" t="str">
         <f>LOOKUP(J41,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M41" s="21">
+      <c r="M41" s="12">
         <f>LOOKUP(J41,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N41" s="21">
+      <c r="N41" s="12">
         <f>LOOKUP(J41,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O41" s="21">
+      <c r="O41" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C42" s="23">
+      <c r="C42" s="14">
         <v>5</v>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="14">
         <v>5</v>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="14">
         <v>30.6</v>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="14">
         <v>52</v>
       </c>
-      <c r="G42" s="23">
+      <c r="G42" s="14">
         <v>49</v>
       </c>
-      <c r="H42" s="23">
+      <c r="H42" s="14">
         <v>54</v>
       </c>
-      <c r="I42" s="18">
-        <v>0</v>
-      </c>
-      <c r="J42" s="22" t="s">
+      <c r="I42" s="12">
+        <v>0</v>
+      </c>
+      <c r="J42" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="K42" s="17">
+      <c r="K42" s="12">
         <v>1</v>
       </c>
-      <c r="L42" s="21" t="str">
+      <c r="L42" s="12" t="str">
         <f>LOOKUP(J42,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M42" s="21">
+      <c r="M42" s="12">
         <f>LOOKUP(J42,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N42" s="21">
+      <c r="N42" s="12">
         <f>LOOKUP(J42,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O42" s="21">
+      <c r="O42" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C43" s="23">
+      <c r="C43" s="14">
         <v>5</v>
       </c>
-      <c r="D43" s="23">
+      <c r="D43" s="14">
         <v>52</v>
       </c>
-      <c r="E43" s="23">
+      <c r="E43" s="14">
         <v>27.5</v>
       </c>
-      <c r="F43" s="23">
+      <c r="F43" s="14">
         <v>15</v>
       </c>
-      <c r="G43" s="23">
+      <c r="G43" s="14">
         <v>53</v>
       </c>
-      <c r="H43" s="23">
+      <c r="H43" s="14">
         <v>17</v>
       </c>
-      <c r="I43" s="18">
-        <v>0</v>
-      </c>
-      <c r="J43" s="22" t="s">
+      <c r="I43" s="12">
+        <v>0</v>
+      </c>
+      <c r="J43" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="K43" s="17">
+      <c r="K43" s="12">
         <v>1</v>
       </c>
-      <c r="L43" s="21" t="str">
+      <c r="L43" s="12" t="str">
         <f>LOOKUP(J43,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M43" s="21">
+      <c r="M43" s="12">
         <f>LOOKUP(J43,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N43" s="21">
+      <c r="N43" s="12">
         <f>LOOKUP(J43,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O43" s="21">
+      <c r="O43" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="22" t="s">
+      <c r="A44" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C44" s="23">
+      <c r="C44" s="14">
         <v>12</v>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="14">
         <v>57</v>
       </c>
-      <c r="E44" s="23">
+      <c r="E44" s="14">
         <v>2.4</v>
       </c>
-      <c r="F44" s="23">
+      <c r="F44" s="14">
         <v>22</v>
       </c>
-      <c r="G44" s="23">
+      <c r="G44" s="14">
         <v>1</v>
       </c>
-      <c r="H44" s="23">
+      <c r="H44" s="14">
         <v>56</v>
       </c>
-      <c r="I44" s="18">
-        <v>0</v>
-      </c>
-      <c r="J44" s="22" t="s">
+      <c r="I44" s="12">
+        <v>0</v>
+      </c>
+      <c r="J44" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="K44" s="17">
+      <c r="K44" s="12">
         <v>1</v>
       </c>
-      <c r="L44" s="21" t="str">
+      <c r="L44" s="12" t="str">
         <f>LOOKUP(J44,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M44" s="21">
+      <c r="M44" s="12">
         <f>LOOKUP(J44,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N44" s="21">
+      <c r="N44" s="12">
         <f>LOOKUP(J44,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O44" s="21">
+      <c r="O44" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="22" t="s">
+      <c r="A45" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C45" s="23">
+      <c r="C45" s="14">
         <v>13</v>
       </c>
-      <c r="D45" s="23">
+      <c r="D45" s="14">
         <v>16</v>
       </c>
-      <c r="E45" s="23">
+      <c r="E45" s="14">
         <v>22</v>
       </c>
-      <c r="F45" s="23">
+      <c r="F45" s="14">
         <v>29</v>
       </c>
-      <c r="G45" s="23">
+      <c r="G45" s="14">
         <v>5</v>
       </c>
-      <c r="H45" s="23">
+      <c r="H45" s="14">
         <v>57</v>
       </c>
-      <c r="I45" s="18">
-        <v>0</v>
-      </c>
-      <c r="J45" s="22" t="s">
+      <c r="I45" s="12">
+        <v>0</v>
+      </c>
+      <c r="J45" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="K45" s="17">
+      <c r="K45" s="12">
         <v>1</v>
       </c>
-      <c r="L45" s="21" t="str">
+      <c r="L45" s="12" t="str">
         <f>LOOKUP(J45,Survey_Info!A:A,Survey_Info!G:G)</f>
         <v>TTAG</v>
       </c>
-      <c r="M45" s="21">
+      <c r="M45" s="12">
         <f>LOOKUP(J45,Survey_Info!A:A,Survey_Info!D:D)</f>
         <v>10000</v>
       </c>
-      <c r="N45" s="21">
+      <c r="N45" s="12">
         <f>LOOKUP(J45,Survey_Info!A:A, Survey_Info!J:J)</f>
         <v>1000</v>
       </c>
-      <c r="O45" s="21">
+      <c r="O45" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="22"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="23"/>
-      <c r="I46" s="23"/>
-      <c r="J46" s="22"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="21"/>
-      <c r="M46" s="21"/>
-      <c r="N46" s="21"/>
-      <c r="O46" s="21"/>
+      <c r="A46" s="14"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="12"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" s="22"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="23"/>
-      <c r="G47" s="23"/>
-      <c r="H47" s="23"/>
-      <c r="I47" s="23"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="21"/>
-      <c r="M47" s="21"/>
-      <c r="N47" s="21"/>
-      <c r="O47" s="21"/>
+      <c r="A47" s="14"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
+      <c r="M47" s="12"/>
+      <c r="N47" s="12"/>
+      <c r="O47" s="12"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" s="22"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="23"/>
-      <c r="G48" s="23"/>
-      <c r="H48" s="23"/>
-      <c r="I48" s="23"/>
-      <c r="J48" s="22"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="21"/>
-      <c r="M48" s="21"/>
-      <c r="N48" s="21"/>
-      <c r="O48" s="21"/>
+      <c r="A48" s="14"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="12"/>
+      <c r="N48" s="12"/>
+      <c r="O48" s="12"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="22"/>
-      <c r="B49" s="23"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
-      <c r="J49" s="22"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="21"/>
-      <c r="M49" s="21"/>
-      <c r="N49" s="21"/>
-      <c r="O49" s="21"/>
+      <c r="A49" s="14"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="12"/>
+      <c r="L49" s="12"/>
+      <c r="M49" s="12"/>
+      <c r="N49" s="12"/>
+      <c r="O49" s="12"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="22"/>
-      <c r="B50" s="23"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="23"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="23"/>
-      <c r="J50" s="22"/>
-      <c r="K50" s="17"/>
-      <c r="L50" s="21"/>
-      <c r="M50" s="21"/>
-      <c r="N50" s="21"/>
-      <c r="O50" s="21"/>
+      <c r="A50" s="14"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="12"/>
+      <c r="L50" s="12"/>
+      <c r="M50" s="12"/>
+      <c r="N50" s="12"/>
+      <c r="O50" s="12"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="22"/>
-      <c r="B51" s="23"/>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
-      <c r="H51" s="23"/>
-      <c r="I51" s="23"/>
-      <c r="J51" s="22"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="21"/>
-      <c r="M51" s="21"/>
-      <c r="N51" s="21"/>
-      <c r="O51" s="21"/>
+      <c r="A51" s="14"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="12"/>
+      <c r="L51" s="12"/>
+      <c r="M51" s="12"/>
+      <c r="N51" s="12"/>
+      <c r="O51" s="12"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="22"/>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="23"/>
-      <c r="J52" s="22"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="21"/>
-      <c r="M52" s="21"/>
-      <c r="N52" s="21"/>
-      <c r="O52" s="21"/>
+      <c r="A52" s="14"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="12"/>
+      <c r="L52" s="12"/>
+      <c r="M52" s="12"/>
+      <c r="N52" s="12"/>
+      <c r="O52" s="12"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="22"/>
-      <c r="B53" s="23"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="23"/>
-      <c r="G53" s="23"/>
-      <c r="H53" s="23"/>
-      <c r="I53" s="23"/>
-      <c r="J53" s="22"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="21"/>
-      <c r="M53" s="21"/>
-      <c r="N53" s="21"/>
-      <c r="O53" s="21"/>
+      <c r="A53" s="14"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="12"/>
+      <c r="L53" s="12"/>
+      <c r="M53" s="12"/>
+      <c r="N53" s="12"/>
+      <c r="O53" s="12"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="22"/>
-      <c r="B54" s="23"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="23"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="23"/>
-      <c r="G54" s="23"/>
-      <c r="H54" s="23"/>
-      <c r="I54" s="23"/>
-      <c r="J54" s="22"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="21"/>
-      <c r="M54" s="21"/>
-      <c r="N54" s="21"/>
-      <c r="O54" s="21"/>
+      <c r="A54" s="14"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12"/>
+      <c r="N54" s="12"/>
+      <c r="O54" s="12"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="22"/>
-      <c r="B55" s="23"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
-      <c r="H55" s="23"/>
-      <c r="I55" s="23"/>
-      <c r="J55" s="22"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="21"/>
-      <c r="M55" s="21"/>
-      <c r="N55" s="21"/>
-      <c r="O55" s="21"/>
+      <c r="A55" s="14"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="12"/>
+      <c r="L55" s="12"/>
+      <c r="M55" s="12"/>
+      <c r="N55" s="12"/>
+      <c r="O55" s="12"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="22"/>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="23"/>
-      <c r="J56" s="22"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="21"/>
-      <c r="M56" s="21"/>
-      <c r="N56" s="21"/>
-      <c r="O56" s="21"/>
+      <c r="A56" s="14"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="12"/>
+      <c r="L56" s="12"/>
+      <c r="M56" s="12"/>
+      <c r="N56" s="12"/>
+      <c r="O56" s="12"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="23"/>
-      <c r="E57" s="23"/>
-      <c r="F57" s="23"/>
-      <c r="G57" s="23"/>
-      <c r="H57" s="23"/>
-      <c r="I57" s="23"/>
-      <c r="J57" s="22"/>
-      <c r="K57" s="17"/>
-      <c r="L57" s="21"/>
-      <c r="M57" s="21"/>
-      <c r="N57" s="21"/>
-      <c r="O57" s="21"/>
+      <c r="A57" s="14"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="12"/>
+      <c r="L57" s="12"/>
+      <c r="M57" s="12"/>
+      <c r="N57" s="12"/>
+      <c r="O57" s="12"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="22"/>
-      <c r="B58" s="23"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
-      <c r="H58" s="23"/>
-      <c r="I58" s="23"/>
-      <c r="J58" s="22"/>
-      <c r="K58" s="17"/>
-      <c r="L58" s="21"/>
-      <c r="M58" s="21"/>
-      <c r="N58" s="21"/>
-      <c r="O58" s="21"/>
+      <c r="A58" s="14"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="12"/>
+      <c r="L58" s="12"/>
+      <c r="M58" s="12"/>
+      <c r="N58" s="12"/>
+      <c r="O58" s="12"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="22"/>
-      <c r="B59" s="23"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="23"/>
-      <c r="H59" s="23"/>
-      <c r="I59" s="23"/>
-      <c r="J59" s="22"/>
-      <c r="K59" s="17"/>
-      <c r="L59" s="21"/>
-      <c r="M59" s="21"/>
-      <c r="N59" s="21"/>
-      <c r="O59" s="21"/>
+      <c r="A59" s="14"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="12"/>
+      <c r="L59" s="12"/>
+      <c r="M59" s="12"/>
+      <c r="N59" s="12"/>
+      <c r="O59" s="12"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
-      <c r="C60" s="23"/>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="23"/>
-      <c r="G60" s="23"/>
-      <c r="H60" s="23"/>
-      <c r="I60" s="23"/>
-      <c r="J60" s="22"/>
-      <c r="K60" s="17"/>
-      <c r="L60" s="21"/>
-      <c r="M60" s="21"/>
-      <c r="N60" s="21"/>
-      <c r="O60" s="21"/>
+      <c r="A60" s="14"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="12"/>
+      <c r="L60" s="12"/>
+      <c r="M60" s="12"/>
+      <c r="N60" s="12"/>
+      <c r="O60" s="12"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="22"/>
-      <c r="B61" s="23"/>
-      <c r="C61" s="23"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="23"/>
-      <c r="G61" s="23"/>
-      <c r="H61" s="23"/>
-      <c r="I61" s="23"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="17"/>
-      <c r="L61" s="21"/>
-      <c r="M61" s="21"/>
-      <c r="N61" s="21"/>
-      <c r="O61" s="21"/>
+      <c r="A61" s="14"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="12"/>
+      <c r="L61" s="12"/>
+      <c r="M61" s="12"/>
+      <c r="N61" s="12"/>
+      <c r="O61" s="12"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="22"/>
-      <c r="B62" s="23"/>
-      <c r="C62" s="23"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
-      <c r="H62" s="23"/>
-      <c r="I62" s="23"/>
-      <c r="J62" s="22"/>
-      <c r="K62" s="17"/>
-      <c r="L62" s="21"/>
-      <c r="M62" s="21"/>
-      <c r="N62" s="21"/>
-      <c r="O62" s="21"/>
+      <c r="A62" s="14"/>
+      <c r="B62" s="14"/>
+      <c r="C62" s="14"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="12"/>
+      <c r="L62" s="12"/>
+      <c r="M62" s="12"/>
+      <c r="N62" s="12"/>
+      <c r="O62" s="12"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="22"/>
-      <c r="B63" s="23"/>
-      <c r="C63" s="23"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
-      <c r="H63" s="23"/>
-      <c r="I63" s="23"/>
-      <c r="J63" s="22"/>
-      <c r="K63" s="17"/>
-      <c r="L63" s="21"/>
-      <c r="M63" s="21"/>
-      <c r="N63" s="21"/>
-      <c r="O63" s="21"/>
+      <c r="A63" s="14"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="12"/>
+      <c r="L63" s="12"/>
+      <c r="M63" s="12"/>
+      <c r="N63" s="12"/>
+      <c r="O63" s="12"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="22"/>
-      <c r="B64" s="23"/>
-      <c r="C64" s="23"/>
-      <c r="D64" s="23"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="23"/>
-      <c r="J64" s="22"/>
-      <c r="K64" s="17"/>
-      <c r="L64" s="21"/>
-      <c r="M64" s="21"/>
-      <c r="N64" s="21"/>
-      <c r="O64" s="21"/>
+      <c r="A64" s="14"/>
+      <c r="B64" s="14"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="12"/>
+      <c r="L64" s="12"/>
+      <c r="M64" s="12"/>
+      <c r="N64" s="12"/>
+      <c r="O64" s="12"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A65" s="22"/>
-      <c r="B65" s="23"/>
-      <c r="C65" s="23"/>
-      <c r="D65" s="23"/>
-      <c r="E65" s="23"/>
-      <c r="F65" s="23"/>
-      <c r="G65" s="23"/>
-      <c r="H65" s="23"/>
-      <c r="I65" s="23"/>
-      <c r="J65" s="22"/>
-      <c r="K65" s="17"/>
-      <c r="L65" s="21"/>
-      <c r="M65" s="21"/>
-      <c r="N65" s="21"/>
-      <c r="O65" s="21"/>
+      <c r="A65" s="14"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+      <c r="K65" s="12"/>
+      <c r="L65" s="12"/>
+      <c r="M65" s="12"/>
+      <c r="N65" s="12"/>
+      <c r="O65" s="12"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A66" s="22"/>
-      <c r="B66" s="23"/>
-      <c r="C66" s="23"/>
-      <c r="D66" s="23"/>
-      <c r="E66" s="23"/>
-      <c r="F66" s="23"/>
-      <c r="G66" s="23"/>
-      <c r="H66" s="23"/>
-      <c r="I66" s="23"/>
-      <c r="J66" s="22"/>
-      <c r="K66" s="17"/>
-      <c r="L66" s="21"/>
-      <c r="M66" s="21"/>
-      <c r="N66" s="21"/>
-      <c r="O66" s="21"/>
+      <c r="A66" s="14"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+      <c r="K66" s="12"/>
+      <c r="L66" s="12"/>
+      <c r="M66" s="12"/>
+      <c r="N66" s="12"/>
+      <c r="O66" s="12"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A67" s="22"/>
-      <c r="B67" s="23"/>
-      <c r="C67" s="23"/>
-      <c r="D67" s="23"/>
-      <c r="E67" s="23"/>
-      <c r="F67" s="23"/>
-      <c r="G67" s="23"/>
-      <c r="H67" s="23"/>
-      <c r="I67" s="23"/>
-      <c r="J67" s="22"/>
-      <c r="K67" s="17"/>
-      <c r="L67" s="21"/>
-      <c r="M67" s="21"/>
-      <c r="N67" s="21"/>
-      <c r="O67" s="21"/>
+      <c r="A67" s="14"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+      <c r="K67" s="12"/>
+      <c r="L67" s="12"/>
+      <c r="M67" s="12"/>
+      <c r="N67" s="12"/>
+      <c r="O67" s="12"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A68" s="22"/>
-      <c r="B68" s="23"/>
-      <c r="C68" s="23"/>
-      <c r="D68" s="23"/>
-      <c r="E68" s="23"/>
-      <c r="F68" s="23"/>
-      <c r="G68" s="23"/>
-      <c r="H68" s="23"/>
-      <c r="I68" s="23"/>
-      <c r="J68" s="22"/>
-      <c r="K68" s="17"/>
-      <c r="L68" s="21"/>
-      <c r="M68" s="21"/>
-      <c r="N68" s="21"/>
-      <c r="O68" s="21"/>
+      <c r="A68" s="14"/>
+      <c r="B68" s="14"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="12"/>
+      <c r="L68" s="12"/>
+      <c r="M68" s="12"/>
+      <c r="N68" s="12"/>
+      <c r="O68" s="12"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="22"/>
-      <c r="B69" s="23"/>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="23"/>
-      <c r="H69" s="23"/>
-      <c r="I69" s="23"/>
-      <c r="J69" s="22"/>
-      <c r="K69" s="17"/>
-      <c r="L69" s="21"/>
-      <c r="M69" s="21"/>
-      <c r="N69" s="21"/>
-      <c r="O69" s="21"/>
+      <c r="A69" s="14"/>
+      <c r="B69" s="14"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="12"/>
+      <c r="L69" s="12"/>
+      <c r="M69" s="12"/>
+      <c r="N69" s="12"/>
+      <c r="O69" s="12"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="22"/>
-      <c r="B70" s="23"/>
-      <c r="C70" s="23"/>
-      <c r="D70" s="23"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="23"/>
-      <c r="G70" s="23"/>
-      <c r="H70" s="23"/>
-      <c r="I70" s="23"/>
-      <c r="J70" s="22"/>
-      <c r="K70" s="17"/>
-      <c r="L70" s="21"/>
-      <c r="M70" s="21"/>
-      <c r="N70" s="21"/>
-      <c r="O70" s="21"/>
+      <c r="A70" s="14"/>
+      <c r="B70" s="14"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="12"/>
+      <c r="L70" s="12"/>
+      <c r="M70" s="12"/>
+      <c r="N70" s="12"/>
+      <c r="O70" s="12"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="22"/>
-      <c r="B71" s="23"/>
-      <c r="C71" s="23"/>
-      <c r="D71" s="23"/>
-      <c r="E71" s="23"/>
-      <c r="F71" s="23"/>
-      <c r="G71" s="23"/>
-      <c r="H71" s="23"/>
-      <c r="I71" s="23"/>
-      <c r="J71" s="22"/>
-      <c r="K71" s="17"/>
-      <c r="L71" s="21"/>
-      <c r="M71" s="21"/>
-      <c r="N71" s="21"/>
-      <c r="O71" s="21"/>
+      <c r="A71" s="14"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="12"/>
+      <c r="L71" s="12"/>
+      <c r="M71" s="12"/>
+      <c r="N71" s="12"/>
+      <c r="O71" s="12"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A72" s="22"/>
-      <c r="B72" s="23"/>
-      <c r="C72" s="23"/>
-      <c r="D72" s="23"/>
-      <c r="E72" s="23"/>
-      <c r="F72" s="23"/>
-      <c r="G72" s="23"/>
-      <c r="H72" s="23"/>
-      <c r="I72" s="23"/>
-      <c r="J72" s="22"/>
-      <c r="K72" s="17"/>
-      <c r="L72" s="21"/>
-      <c r="M72" s="21"/>
-      <c r="N72" s="21"/>
-      <c r="O72" s="21"/>
+      <c r="A72" s="14"/>
+      <c r="B72" s="14"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="12"/>
+      <c r="L72" s="12"/>
+      <c r="M72" s="12"/>
+      <c r="N72" s="12"/>
+      <c r="O72" s="12"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A73" s="22"/>
-      <c r="B73" s="23"/>
-      <c r="C73" s="23"/>
-      <c r="D73" s="23"/>
-      <c r="E73" s="23"/>
-      <c r="F73" s="23"/>
-      <c r="G73" s="23"/>
-      <c r="H73" s="23"/>
-      <c r="I73" s="23"/>
-      <c r="J73" s="22"/>
-      <c r="K73" s="17"/>
-      <c r="L73" s="21"/>
-      <c r="M73" s="21"/>
-      <c r="N73" s="21"/>
-      <c r="O73" s="21"/>
+      <c r="A73" s="14"/>
+      <c r="B73" s="14"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="12"/>
+      <c r="L73" s="12"/>
+      <c r="M73" s="12"/>
+      <c r="N73" s="12"/>
+      <c r="O73" s="12"/>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A74" s="22"/>
-      <c r="B74" s="23"/>
-      <c r="C74" s="23"/>
-      <c r="D74" s="23"/>
-      <c r="E74" s="23"/>
-      <c r="F74" s="23"/>
-      <c r="G74" s="23"/>
-      <c r="H74" s="23"/>
-      <c r="I74" s="23"/>
-      <c r="J74" s="22"/>
-      <c r="K74" s="17"/>
-      <c r="L74" s="21"/>
-      <c r="M74" s="21"/>
-      <c r="N74" s="21"/>
-      <c r="O74" s="21"/>
+      <c r="A74" s="14"/>
+      <c r="B74" s="14"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="12"/>
+      <c r="L74" s="12"/>
+      <c r="M74" s="12"/>
+      <c r="N74" s="12"/>
+      <c r="O74" s="12"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A75" s="22"/>
-      <c r="B75" s="23"/>
-      <c r="C75" s="23"/>
-      <c r="D75" s="23"/>
-      <c r="E75" s="23"/>
-      <c r="F75" s="23"/>
-      <c r="G75" s="23"/>
-      <c r="H75" s="23"/>
-      <c r="I75" s="23"/>
-      <c r="J75" s="22"/>
-      <c r="K75" s="17"/>
-      <c r="L75" s="21"/>
-      <c r="M75" s="21"/>
-      <c r="N75" s="21"/>
-      <c r="O75" s="21"/>
+      <c r="A75" s="14"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+      <c r="K75" s="12"/>
+      <c r="L75" s="12"/>
+      <c r="M75" s="12"/>
+      <c r="N75" s="12"/>
+      <c r="O75" s="12"/>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A76" s="22"/>
-      <c r="B76" s="23"/>
-      <c r="C76" s="23"/>
-      <c r="D76" s="23"/>
-      <c r="E76" s="23"/>
-      <c r="F76" s="23"/>
-      <c r="G76" s="23"/>
-      <c r="H76" s="23"/>
-      <c r="I76" s="23"/>
-      <c r="J76" s="22"/>
-      <c r="K76" s="17"/>
-      <c r="L76" s="21"/>
-      <c r="M76" s="21"/>
-      <c r="N76" s="21"/>
-      <c r="O76" s="21"/>
+      <c r="A76" s="14"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="14"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="14"/>
+      <c r="H76" s="14"/>
+      <c r="I76" s="14"/>
+      <c r="J76" s="14"/>
+      <c r="K76" s="12"/>
+      <c r="L76" s="12"/>
+      <c r="M76" s="12"/>
+      <c r="N76" s="12"/>
+      <c r="O76" s="12"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="22"/>
-      <c r="B77" s="23"/>
-      <c r="C77" s="23"/>
-      <c r="D77" s="23"/>
-      <c r="E77" s="23"/>
-      <c r="F77" s="23"/>
-      <c r="G77" s="23"/>
-      <c r="H77" s="23"/>
-      <c r="I77" s="23"/>
-      <c r="J77" s="22"/>
-      <c r="K77" s="17"/>
-      <c r="L77" s="21"/>
-      <c r="M77" s="21"/>
-      <c r="N77" s="21"/>
-      <c r="O77" s="21"/>
+      <c r="A77" s="14"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="14"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="14"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+      <c r="K77" s="12"/>
+      <c r="L77" s="12"/>
+      <c r="M77" s="12"/>
+      <c r="N77" s="12"/>
+      <c r="O77" s="12"/>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A78" s="22"/>
-      <c r="B78" s="23"/>
-      <c r="C78" s="23"/>
-      <c r="D78" s="23"/>
-      <c r="E78" s="23"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="23"/>
-      <c r="H78" s="23"/>
-      <c r="I78" s="23"/>
-      <c r="J78" s="22"/>
-      <c r="K78" s="17"/>
-      <c r="L78" s="21"/>
-      <c r="M78" s="21"/>
-      <c r="N78" s="21"/>
-      <c r="O78" s="21"/>
+      <c r="A78" s="14"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="14"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+      <c r="K78" s="12"/>
+      <c r="L78" s="12"/>
+      <c r="M78" s="12"/>
+      <c r="N78" s="12"/>
+      <c r="O78" s="12"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A79" s="22"/>
-      <c r="B79" s="23"/>
-      <c r="C79" s="23"/>
-      <c r="D79" s="23"/>
-      <c r="E79" s="23"/>
-      <c r="F79" s="23"/>
-      <c r="G79" s="23"/>
-      <c r="H79" s="23"/>
-      <c r="I79" s="23"/>
-      <c r="J79" s="22"/>
-      <c r="K79" s="17"/>
-      <c r="L79" s="21"/>
-      <c r="M79" s="21"/>
-      <c r="N79" s="21"/>
-      <c r="O79" s="21"/>
+      <c r="A79" s="14"/>
+      <c r="B79" s="14"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+      <c r="K79" s="12"/>
+      <c r="L79" s="12"/>
+      <c r="M79" s="12"/>
+      <c r="N79" s="12"/>
+      <c r="O79" s="12"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A80" s="22"/>
-      <c r="B80" s="23"/>
-      <c r="C80" s="23"/>
-      <c r="D80" s="23"/>
-      <c r="E80" s="23"/>
-      <c r="F80" s="23"/>
-      <c r="G80" s="23"/>
-      <c r="H80" s="23"/>
-      <c r="I80" s="23"/>
-      <c r="J80" s="22"/>
-      <c r="K80" s="17"/>
-      <c r="L80" s="21"/>
-      <c r="M80" s="21"/>
-      <c r="N80" s="21"/>
-      <c r="O80" s="21"/>
+      <c r="A80" s="14"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="14"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="14"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="14"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14"/>
+      <c r="K80" s="12"/>
+      <c r="L80" s="12"/>
+      <c r="M80" s="12"/>
+      <c r="N80" s="12"/>
+      <c r="O80" s="12"/>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A81" s="22"/>
-      <c r="B81" s="23"/>
-      <c r="C81" s="23"/>
-      <c r="D81" s="23"/>
-      <c r="E81" s="23"/>
-      <c r="F81" s="23"/>
-      <c r="G81" s="23"/>
-      <c r="H81" s="23"/>
-      <c r="I81" s="23"/>
-      <c r="J81" s="22"/>
-      <c r="K81" s="17"/>
-      <c r="L81" s="21"/>
-      <c r="M81" s="21"/>
-      <c r="N81" s="21"/>
-      <c r="O81" s="21"/>
+      <c r="A81" s="14"/>
+      <c r="B81" s="14"/>
+      <c r="C81" s="14"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+      <c r="K81" s="12"/>
+      <c r="L81" s="12"/>
+      <c r="M81" s="12"/>
+      <c r="N81" s="12"/>
+      <c r="O81" s="12"/>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A82" s="22"/>
-      <c r="B82" s="23"/>
-      <c r="C82" s="23"/>
-      <c r="D82" s="23"/>
-      <c r="E82" s="23"/>
-      <c r="F82" s="23"/>
-      <c r="G82" s="23"/>
-      <c r="H82" s="23"/>
-      <c r="I82" s="23"/>
-      <c r="J82" s="22"/>
-      <c r="K82" s="17"/>
-      <c r="L82" s="21"/>
-      <c r="M82" s="21"/>
-      <c r="N82" s="21"/>
-      <c r="O82" s="21"/>
+      <c r="A82" s="14"/>
+      <c r="B82" s="14"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+      <c r="K82" s="12"/>
+      <c r="L82" s="12"/>
+      <c r="M82" s="12"/>
+      <c r="N82" s="12"/>
+      <c r="O82" s="12"/>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A83" s="22"/>
-      <c r="B83" s="23"/>
-      <c r="C83" s="23"/>
-      <c r="D83" s="23"/>
-      <c r="E83" s="23"/>
-      <c r="F83" s="23"/>
-      <c r="G83" s="23"/>
-      <c r="H83" s="23"/>
-      <c r="I83" s="23"/>
-      <c r="J83" s="22"/>
-      <c r="K83" s="17"/>
-      <c r="L83" s="21"/>
-      <c r="M83" s="21"/>
-      <c r="N83" s="21"/>
-      <c r="O83" s="21"/>
+      <c r="A83" s="14"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
+      <c r="K83" s="12"/>
+      <c r="L83" s="12"/>
+      <c r="M83" s="12"/>
+      <c r="N83" s="12"/>
+      <c r="O83" s="12"/>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A84" s="22"/>
-      <c r="B84" s="23"/>
-      <c r="C84" s="23"/>
-      <c r="D84" s="23"/>
-      <c r="E84" s="23"/>
-      <c r="F84" s="23"/>
-      <c r="G84" s="23"/>
-      <c r="H84" s="23"/>
-      <c r="I84" s="23"/>
-      <c r="J84" s="22"/>
-      <c r="K84" s="17"/>
-      <c r="L84" s="21"/>
-      <c r="M84" s="21"/>
-      <c r="N84" s="21"/>
-      <c r="O84" s="21"/>
+      <c r="A84" s="14"/>
+      <c r="B84" s="14"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+      <c r="K84" s="12"/>
+      <c r="L84" s="12"/>
+      <c r="M84" s="12"/>
+      <c r="N84" s="12"/>
+      <c r="O84" s="12"/>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A85" s="22"/>
-      <c r="B85" s="23"/>
-      <c r="C85" s="23"/>
-      <c r="D85" s="23"/>
-      <c r="E85" s="23"/>
-      <c r="F85" s="23"/>
-      <c r="G85" s="23"/>
-      <c r="H85" s="23"/>
-      <c r="I85" s="23"/>
-      <c r="J85" s="22"/>
-      <c r="K85" s="17"/>
-      <c r="L85" s="21"/>
-      <c r="M85" s="21"/>
-      <c r="N85" s="21"/>
-      <c r="O85" s="21"/>
+      <c r="A85" s="14"/>
+      <c r="B85" s="14"/>
+      <c r="C85" s="14"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+      <c r="K85" s="12"/>
+      <c r="L85" s="12"/>
+      <c r="M85" s="12"/>
+      <c r="N85" s="12"/>
+      <c r="O85" s="12"/>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A86" s="22"/>
-      <c r="B86" s="23"/>
-      <c r="C86" s="23"/>
-      <c r="D86" s="23"/>
-      <c r="E86" s="23"/>
-      <c r="F86" s="23"/>
-      <c r="G86" s="23"/>
-      <c r="H86" s="23"/>
-      <c r="I86" s="23"/>
-      <c r="J86" s="22"/>
-      <c r="K86" s="17"/>
-      <c r="L86" s="21"/>
-      <c r="M86" s="21"/>
-      <c r="N86" s="21"/>
-      <c r="O86" s="21"/>
+      <c r="A86" s="14"/>
+      <c r="B86" s="14"/>
+      <c r="C86" s="14"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="14"/>
+      <c r="K86" s="12"/>
+      <c r="L86" s="12"/>
+      <c r="M86" s="12"/>
+      <c r="N86" s="12"/>
+      <c r="O86" s="12"/>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A87" s="22"/>
-      <c r="B87" s="23"/>
-      <c r="C87" s="23"/>
-      <c r="D87" s="23"/>
-      <c r="E87" s="23"/>
-      <c r="F87" s="23"/>
-      <c r="G87" s="23"/>
-      <c r="H87" s="23"/>
-      <c r="I87" s="23"/>
-      <c r="J87" s="22"/>
-      <c r="K87" s="17"/>
-      <c r="L87" s="21"/>
-      <c r="M87" s="21"/>
-      <c r="N87" s="21"/>
-      <c r="O87" s="21"/>
+      <c r="A87" s="14"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+      <c r="K87" s="12"/>
+      <c r="L87" s="12"/>
+      <c r="M87" s="12"/>
+      <c r="N87" s="12"/>
+      <c r="O87" s="12"/>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A88" s="22"/>
-      <c r="B88" s="23"/>
-      <c r="C88" s="23"/>
-      <c r="D88" s="23"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="23"/>
-      <c r="G88" s="23"/>
-      <c r="H88" s="23"/>
-      <c r="I88" s="23"/>
-      <c r="J88" s="22"/>
-      <c r="K88" s="17"/>
-      <c r="L88" s="21"/>
-      <c r="M88" s="21"/>
-      <c r="N88" s="21"/>
-      <c r="O88" s="21"/>
+      <c r="A88" s="14"/>
+      <c r="B88" s="14"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="14"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="14"/>
+      <c r="K88" s="12"/>
+      <c r="L88" s="12"/>
+      <c r="M88" s="12"/>
+      <c r="N88" s="12"/>
+      <c r="O88" s="12"/>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A89" s="22"/>
-      <c r="B89" s="23"/>
-      <c r="C89" s="23"/>
-      <c r="D89" s="23"/>
-      <c r="E89" s="23"/>
-      <c r="F89" s="23"/>
-      <c r="G89" s="23"/>
-      <c r="H89" s="23"/>
-      <c r="I89" s="23"/>
-      <c r="J89" s="22"/>
-      <c r="K89" s="17"/>
-      <c r="L89" s="21"/>
-      <c r="M89" s="21"/>
-      <c r="N89" s="21"/>
-      <c r="O89" s="21"/>
+      <c r="A89" s="14"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="14"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="14"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="14"/>
+      <c r="K89" s="12"/>
+      <c r="L89" s="12"/>
+      <c r="M89" s="12"/>
+      <c r="N89" s="12"/>
+      <c r="O89" s="12"/>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A90" s="22"/>
-      <c r="B90" s="23"/>
-      <c r="C90" s="23"/>
-      <c r="D90" s="23"/>
-      <c r="E90" s="23"/>
-      <c r="F90" s="23"/>
-      <c r="G90" s="23"/>
-      <c r="H90" s="23"/>
-      <c r="I90" s="23"/>
-      <c r="J90" s="22"/>
-      <c r="K90" s="17"/>
-      <c r="L90" s="21"/>
-      <c r="M90" s="21"/>
-      <c r="N90" s="21"/>
-      <c r="O90" s="21"/>
+      <c r="A90" s="14"/>
+      <c r="B90" s="14"/>
+      <c r="C90" s="14"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
+      <c r="J90" s="14"/>
+      <c r="K90" s="12"/>
+      <c r="L90" s="12"/>
+      <c r="M90" s="12"/>
+      <c r="N90" s="12"/>
+      <c r="O90" s="12"/>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A91" s="22"/>
-      <c r="B91" s="23"/>
-      <c r="C91" s="23"/>
-      <c r="D91" s="23"/>
-      <c r="E91" s="23"/>
-      <c r="F91" s="23"/>
-      <c r="G91" s="23"/>
-      <c r="H91" s="23"/>
-      <c r="I91" s="23"/>
-      <c r="J91" s="22"/>
-      <c r="K91" s="17"/>
-      <c r="L91" s="21"/>
-      <c r="M91" s="21"/>
-      <c r="N91" s="21"/>
-      <c r="O91" s="21"/>
+      <c r="A91" s="14"/>
+      <c r="B91" s="14"/>
+      <c r="C91" s="14"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="14"/>
+      <c r="K91" s="12"/>
+      <c r="L91" s="12"/>
+      <c r="M91" s="12"/>
+      <c r="N91" s="12"/>
+      <c r="O91" s="12"/>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A92" s="22"/>
-      <c r="B92" s="23"/>
-      <c r="C92" s="23"/>
-      <c r="D92" s="23"/>
-      <c r="E92" s="23"/>
-      <c r="F92" s="23"/>
-      <c r="G92" s="23"/>
-      <c r="H92" s="23"/>
-      <c r="I92" s="23"/>
-      <c r="J92" s="22"/>
-      <c r="K92" s="17"/>
-      <c r="L92" s="21"/>
-      <c r="M92" s="21"/>
-      <c r="N92" s="21"/>
-      <c r="O92" s="21"/>
+      <c r="A92" s="14"/>
+      <c r="B92" s="14"/>
+      <c r="C92" s="14"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="14"/>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
+      <c r="J92" s="14"/>
+      <c r="K92" s="12"/>
+      <c r="L92" s="12"/>
+      <c r="M92" s="12"/>
+      <c r="N92" s="12"/>
+      <c r="O92" s="12"/>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A93" s="22"/>
-      <c r="B93" s="23"/>
-      <c r="C93" s="23"/>
-      <c r="D93" s="23"/>
-      <c r="E93" s="23"/>
-      <c r="F93" s="23"/>
-      <c r="G93" s="23"/>
-      <c r="H93" s="23"/>
-      <c r="I93" s="23"/>
-      <c r="J93" s="22"/>
-      <c r="K93" s="17"/>
-      <c r="L93" s="21"/>
-      <c r="M93" s="21"/>
-      <c r="N93" s="21"/>
-      <c r="O93" s="21"/>
+      <c r="A93" s="14"/>
+      <c r="B93" s="14"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="H93" s="14"/>
+      <c r="I93" s="14"/>
+      <c r="J93" s="14"/>
+      <c r="K93" s="12"/>
+      <c r="L93" s="12"/>
+      <c r="M93" s="12"/>
+      <c r="N93" s="12"/>
+      <c r="O93" s="12"/>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A94" s="22"/>
-      <c r="B94" s="23"/>
-      <c r="C94" s="23"/>
-      <c r="D94" s="23"/>
-      <c r="E94" s="23"/>
-      <c r="F94" s="23"/>
-      <c r="G94" s="23"/>
-      <c r="H94" s="23"/>
-      <c r="I94" s="23"/>
-      <c r="J94" s="22"/>
-      <c r="K94" s="17"/>
-      <c r="L94" s="21"/>
-      <c r="M94" s="21"/>
-      <c r="N94" s="21"/>
-      <c r="O94" s="21"/>
+      <c r="A94" s="14"/>
+      <c r="B94" s="14"/>
+      <c r="C94" s="14"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="14"/>
+      <c r="F94" s="14"/>
+      <c r="G94" s="14"/>
+      <c r="H94" s="14"/>
+      <c r="I94" s="14"/>
+      <c r="J94" s="14"/>
+      <c r="K94" s="12"/>
+      <c r="L94" s="12"/>
+      <c r="M94" s="12"/>
+      <c r="N94" s="12"/>
+      <c r="O94" s="12"/>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L95" s="9"/>
+      <c r="L95" s="6"/>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L96" s="9"/>
+      <c r="L96" s="6"/>
     </row>
     <row r="97" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L97" s="9"/>
+      <c r="L97" s="6"/>
     </row>
     <row r="98" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L98" s="9"/>
+      <c r="L98" s="6"/>
     </row>
     <row r="99" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L99" s="9"/>
+      <c r="L99" s="6"/>
     </row>
     <row r="100" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L100" s="9"/>
+      <c r="L100" s="6"/>
     </row>
     <row r="101" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L101" s="9"/>
+      <c r="L101" s="6"/>
     </row>
     <row r="102" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L102" s="9"/>
+      <c r="L102" s="6"/>
     </row>
     <row r="103" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L103" s="9"/>
+      <c r="L103" s="6"/>
     </row>
     <row r="104" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L104" s="9"/>
+      <c r="L104" s="6"/>
     </row>
     <row r="105" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L105" s="9"/>
+      <c r="L105" s="6"/>
     </row>
     <row r="106" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L106" s="9"/>
+      <c r="L106" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4162,45 +4161,45 @@
   <dimension ref="A1:AMJ6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.83203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="1024" width="10.83203125" style="9"/>
+    <col min="1" max="1" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="1024" width="10.83203125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="10" t="s">
         <v>78</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -4208,121 +4207,120 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="13">
         <v>20</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="13">
         <v>4</v>
       </c>
-      <c r="D2" s="24">
+      <c r="D2" s="15">
         <v>100000</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="13">
         <f>D2*C2</f>
         <v>400000</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="13">
         <f>E2*B2</f>
         <v>8000000</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="21">
+      <c r="I2" s="13">
         <v>2</v>
       </c>
-      <c r="J2" s="21">
+      <c r="J2" s="13">
         <v>1000</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="13">
         <v>15</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="13">
         <v>2</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="15">
         <v>100000</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="13">
         <f>D3*C3</f>
         <v>200000</v>
       </c>
-      <c r="F3" s="21">
-        <f>E3*B3</f>
-        <v>3000000</v>
-      </c>
-      <c r="G3" s="21" t="s">
+      <c r="F3" s="13">
+        <v>5000000</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="13">
         <v>1</v>
       </c>
-      <c r="J3" s="21">
-        <v>50000</v>
+      <c r="J3" s="13">
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="13">
         <v>4</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="13">
         <v>2</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="15">
         <v>10000</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="13">
         <f>D4*C4</f>
         <v>20000</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="13">
         <f>E4*B4</f>
         <v>80000</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="13">
         <v>3</v>
       </c>
-      <c r="J4" s="21">
+      <c r="J4" s="13">
         <v>1000</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="25"/>
+      <c r="A6" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4369,27 +4367,27 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
+      <c r="A2" s="17">
         <f>B2*0.9</f>
         <v>307800</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="17">
         <v>342000</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="17">
         <f>(E2+75.7)*0.9</f>
         <v>39.042000000000002</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="17">
         <v>-36.72</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="17">
         <v>-32.32</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="17">
         <v>-48.32</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="17">
         <f>E2</f>
         <v>-32.32</v>
       </c>
@@ -4431,23 +4429,23 @@
       <c r="E1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
-        <v>0</v>
-      </c>
-      <c r="B2" s="26">
+      <c r="A2" s="17">
+        <v>0</v>
+      </c>
+      <c r="B2" s="17">
         <v>200</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="17">
         <v>2</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="17">
         <v>0.13700000000000001</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="17">
         <v>3.125</v>
       </c>
     </row>
@@ -4478,77 +4476,77 @@
       <c r="D1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="27"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="29">
         <v>40.015000000000001</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="29">
         <v>-105.2705</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="30">
         <v>1655</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="29">
         <v>15</v>
       </c>
-      <c r="F2" s="25"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="29">
         <v>40.10078</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="29">
         <v>-83.197509999999994</v>
       </c>
-      <c r="D3" s="1">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D3" s="29">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="29">
         <v>45.854579999999999</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="31">
         <v>-119.63198</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="29">
         <v>1000</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="29">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="29">
         <v>53.778799999999997</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="29">
         <v>-7.3055000000000003</v>
       </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="D5" s="29">
+        <v>0</v>
+      </c>
+      <c r="E5" s="29">
         <v>15</v>
       </c>
     </row>
@@ -4575,7 +4573,7 @@
       <c r="A2">
         <v>-20</v>
       </c>
-      <c r="B2" s="30">
+      <c r="B2" s="19">
         <v>6.5900000000000002E-15</v>
       </c>
     </row>
@@ -5367,7 +5365,7 @@
       <c r="A101">
         <v>-20.117609659999999</v>
       </c>
-      <c r="B101" s="30">
+      <c r="B101" s="19">
         <v>-1.7800000000000001E-14</v>
       </c>
     </row>
@@ -5381,26 +5379,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="17" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
+    <row r="2" spans="1:3" ht="19" x14ac:dyDescent="0.25">
+      <c r="A2" s="17">
         <v>15</v>
       </c>
-      <c r="B2">
-        <v>15</v>
-      </c>
-      <c r="C2">
+      <c r="B2" s="17">
+        <v>90</v>
+      </c>
+      <c r="C2" s="17">
         <v>15</v>
       </c>
     </row>

--- a/Data Files/MANTIS_Mission_Config_v2.xlsx
+++ b/Data Files/MANTIS_Mission_Config_v2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebastianescobar/Desktop/CubeSatMissionPlanner-1/Data Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebastianescobar/Desktop/CubeSatMissionPlanner/Data Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09744BAE-204C-B64C-BB93-13DA765C1459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F93B25-EEFD-CD41-93E5-9675A100DBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8360" yWindow="3280" windowWidth="21760" windowHeight="14380" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3840" yWindow="2260" windowWidth="21760" windowHeight="14380" tabRatio="500" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlanPropagation_Info" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="SAA_Info" sheetId="7" r:id="rId7"/>
     <sheet name="Constraints_Info" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -458,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -522,8 +522,7 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2797,7 +2796,7 @@
         <v>TTAG</v>
       </c>
       <c r="M36" s="12">
-        <v>300</v>
+        <v>10000</v>
       </c>
       <c r="N36" s="12">
         <f>LOOKUP(J36,Survey_Info!A:A, Survey_Info!J:J)</f>
@@ -4482,71 +4481,71 @@
       <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="29">
+      <c r="B2" s="17">
         <v>40.015000000000001</v>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="17">
         <v>-105.2705</v>
       </c>
-      <c r="D2" s="30">
+      <c r="D2" s="29">
         <v>1655</v>
       </c>
-      <c r="E2" s="29">
+      <c r="E2" s="17">
         <v>15</v>
       </c>
       <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="17">
         <v>40.10078</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="17">
         <v>-83.197509999999994</v>
       </c>
-      <c r="D3" s="29">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29">
+      <c r="D3" s="17">
+        <v>0</v>
+      </c>
+      <c r="E3" s="17">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="17">
         <v>45.854579999999999</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="30">
         <v>-119.63198</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="17">
         <v>1000</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="17">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="17">
         <v>53.778799999999997</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="17">
         <v>-7.3055000000000003</v>
       </c>
-      <c r="D5" s="29">
-        <v>0</v>
-      </c>
-      <c r="E5" s="29">
+      <c r="D5" s="17">
+        <v>0</v>
+      </c>
+      <c r="E5" s="17">
         <v>15</v>
       </c>
     </row>
@@ -5401,7 +5400,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="17">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="C2" s="17">
         <v>15</v>

--- a/Data Files/MANTIS_Mission_Config_v2.xlsx
+++ b/Data Files/MANTIS_Mission_Config_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebastianescobar/Desktop/CubeSatMissionPlanner/Data Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F93B25-EEFD-CD41-93E5-9675A100DBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847DEB99-53CE-6D45-9F20-62D733B0F8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="2260" windowWidth="21760" windowHeight="14380" tabRatio="500" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3840" yWindow="2260" windowWidth="21760" windowHeight="14380" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlanPropagation_Info" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="81">
   <si>
     <t>TLE URL</t>
   </si>
@@ -63,9 +63,6 @@
     <t>Timestep [sec]</t>
   </si>
   <si>
-    <t>https://celestrak.org/NORAD/elements/gp.php?GROUP=active&amp;FORMAT=tle</t>
-  </si>
-  <si>
     <t>cute_tle</t>
   </si>
   <si>
@@ -174,90 +171,12 @@
     <t>EV Lac</t>
   </si>
   <si>
-    <t>Tau Ceti</t>
-  </si>
-  <si>
-    <t>Procyon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HD 189733 </t>
-  </si>
-  <si>
     <t>JUMP</t>
   </si>
   <si>
-    <t xml:space="preserve">55 Cnc </t>
-  </si>
-  <si>
-    <t xml:space="preserve">GJ 357 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">L 98-59 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">WASP-178 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">V1298 Tau </t>
-  </si>
-  <si>
-    <t>HD 209458b</t>
-  </si>
-  <si>
-    <t>LTT 1445A</t>
-  </si>
-  <si>
-    <t>GJ 486</t>
-  </si>
-  <si>
-    <t>GJ 367</t>
-  </si>
-  <si>
-    <t>GJ 341</t>
-  </si>
-  <si>
-    <t>GJ 4102</t>
-  </si>
-  <si>
-    <t>TOI-260</t>
-  </si>
-  <si>
-    <t>TOI-776</t>
-  </si>
-  <si>
-    <t>TOI-836</t>
-  </si>
-  <si>
-    <t>TOI-402</t>
-  </si>
-  <si>
-    <t>HD 80606</t>
-  </si>
-  <si>
-    <t>TOI-421</t>
-  </si>
-  <si>
-    <t>WASP-166</t>
-  </si>
-  <si>
-    <t>WASP-121</t>
-  </si>
-  <si>
-    <t>G191-B2B</t>
-  </si>
-  <si>
     <t>Calibration</t>
   </si>
   <si>
-    <t>GD 71</t>
-  </si>
-  <si>
-    <t>GD 153</t>
-  </si>
-  <si>
-    <t>HZ 43</t>
-  </si>
-  <si>
     <t>N Targets</t>
   </si>
   <si>
@@ -364,6 +283,9 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>https://celestrak.org/NORAD/elements/gp.php?CATNR=49263&amp;FORMAT=tle</t>
   </si>
 </sst>
 </file>
@@ -375,7 +297,7 @@
     <numFmt numFmtId="165" formatCode="00"/>
     <numFmt numFmtId="166" formatCode="00.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -413,6 +335,14 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -455,10 +385,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -526,8 +457,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -961,14 +895,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="D2" s="5">
         <v>45748.020833333336</v>
@@ -981,6 +915,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3A%2F%2Fcelestrak.org%2FNORAD%2Felements%2Fgp.php%3FCATNR%3D49263%26FORMAT%3Dtle&amp;data=05%7C02%7CSebastian.Escobar%40lasp.colorado.edu%7Cc8b62e77ac294876c08408de9c9ed44c%7Cb1ddd7831dbc446b878fa7b03478ea9e%7C1%7C0%7C639120403139812220%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=u3QfNw08NJ2Lc8RuYxyuN00h4d4s%2FdYbxVHUa8yHL4o%3D&amp;reserved=0" display="https://nam10.safelinks.protection.outlook.com/?url=https%3A%2F%2Fcelestrak.org%2FNORAD%2Felements%2Fgp.php%3FCATNR%3D49263%26FORMAT%3Dtle&amp;data=05%7C02%7CSebastian.Escobar%40lasp.colorado.edu%7Cc8b62e77ac294876c08408de9c9ed44c%7Cb1ddd7831dbc446b878fa7b03478ea9e%7C1%7C0%7C639120403139812220%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=u3QfNw08NJ2Lc8RuYxyuN00h4d4s%2FdYbxVHUa8yHL4o%3D&amp;reserved=0" xr:uid="{1D51D9A4-B8BF-6D47-8F6C-DF94280B8DEE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -1012,57 +949,57 @@
   <sheetData>
     <row r="1" spans="1:15" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="E1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="F1" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="G1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="H1" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="N1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C2" s="24">
         <v>10</v>
@@ -1086,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K2" s="12">
         <v>1</v>
@@ -1109,10 +1046,10 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C3" s="24">
         <v>18</v>
@@ -1136,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K3" s="12">
         <v>1</v>
@@ -1159,10 +1096,10 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C4" s="24">
         <v>23</v>
@@ -1186,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K4" s="12">
         <v>1</v>
@@ -1209,10 +1146,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C5" s="24">
         <v>1</v>
@@ -1236,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K5" s="12">
         <v>1</v>
@@ -1259,10 +1196,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C6" s="24">
         <v>21</v>
@@ -1286,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K6" s="12">
         <v>1</v>
@@ -1309,10 +1246,10 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C7" s="24">
         <v>6</v>
@@ -1336,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K7" s="12">
         <v>1</v>
@@ -1359,10 +1296,10 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C8" s="24">
         <v>5</v>
@@ -1386,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K8" s="12">
         <v>1</v>
@@ -1409,10 +1346,10 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C9" s="24">
         <v>4</v>
@@ -1436,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K9" s="12">
         <v>1</v>
@@ -1459,10 +1396,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C10" s="24">
         <v>10</v>
@@ -1486,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K10" s="12">
         <v>1</v>
@@ -1509,10 +1446,10 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C11" s="24">
         <v>3</v>
@@ -1536,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K11" s="12">
         <v>1</v>
@@ -1559,10 +1496,10 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C12" s="24">
         <v>22</v>
@@ -1586,7 +1523,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K12" s="12">
         <v>1</v>
@@ -1609,10 +1546,10 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C13" s="24">
         <v>4</v>
@@ -1636,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K13" s="12">
         <v>1</v>
@@ -1659,10 +1596,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C14" s="24">
         <v>8</v>
@@ -1686,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K14" s="12">
         <v>1</v>
@@ -1709,10 +1646,10 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C15" s="24">
         <v>4</v>
@@ -1736,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K15" s="12">
         <v>1</v>
@@ -1759,10 +1696,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C16" s="14">
         <v>9</v>
@@ -1786,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K16" s="12">
         <v>1</v>
@@ -1809,10 +1746,10 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C17" s="14">
         <v>13</v>
@@ -1836,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K17" s="12">
         <v>1</v>
@@ -1859,10 +1796,10 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C18" s="14">
         <v>4</v>
@@ -1886,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K18" s="12">
         <v>1</v>
@@ -1909,10 +1846,10 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C19" s="14">
         <v>22</v>
@@ -1936,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K19" s="12">
         <v>1</v>
@@ -1958,1303 +1895,446 @@
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
-        <v>44</v>
-      </c>
-      <c r="E20" s="14">
-        <v>4.3800940711717802</v>
-      </c>
-      <c r="F20" s="14">
-        <v>-15</v>
-      </c>
-      <c r="G20" s="14">
-        <v>56</v>
-      </c>
-      <c r="H20" s="14">
-        <v>32.357259787263501</v>
-      </c>
-      <c r="I20" s="12">
-        <v>0</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="K20" s="12">
-        <v>1</v>
-      </c>
-      <c r="L20" s="12" t="str">
-        <f>LOOKUP(J20,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M20" s="12">
-        <f>LOOKUP(J20,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N20" s="12">
-        <f>LOOKUP(J20,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O20" s="12">
-        <v>0</v>
-      </c>
+      <c r="A20" s="14"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" s="14">
-        <v>7</v>
-      </c>
-      <c r="D21" s="14">
-        <v>39</v>
-      </c>
-      <c r="E21" s="14">
-        <v>17.7574773317458</v>
-      </c>
-      <c r="F21" s="14">
-        <v>5</v>
-      </c>
-      <c r="G21" s="14">
-        <v>14</v>
-      </c>
-      <c r="H21" s="14">
-        <v>14.713134425050599</v>
-      </c>
-      <c r="I21" s="12">
-        <v>0</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" s="12">
-        <v>1</v>
-      </c>
-      <c r="L21" s="12" t="str">
-        <f>LOOKUP(J21,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M21" s="12">
-        <f>LOOKUP(J21,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N21" s="12">
-        <f>LOOKUP(J21,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O21" s="12">
-        <v>0</v>
-      </c>
+      <c r="A21" s="14"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22" s="14">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
-        <v>0</v>
-      </c>
-      <c r="E22" s="14">
-        <v>43.712899999999998</v>
-      </c>
-      <c r="F22" s="14">
-        <v>22</v>
-      </c>
-      <c r="G22" s="14">
-        <v>42</v>
-      </c>
-      <c r="H22" s="14">
-        <v>39.073</v>
-      </c>
-      <c r="I22" s="12">
-        <v>0</v>
-      </c>
-      <c r="J22" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K22" s="12">
-        <v>1</v>
-      </c>
-      <c r="L22" s="12" t="str">
-        <f>LOOKUP(J22,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M22" s="12">
-        <f>LOOKUP(J22,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N22" s="12">
-        <f>LOOKUP(J22,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O22" s="12">
-        <v>0</v>
-      </c>
+      <c r="A22" s="14"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C23" s="14">
-        <v>8</v>
-      </c>
-      <c r="D23" s="14">
-        <v>52</v>
-      </c>
-      <c r="E23" s="14">
-        <v>35.811100000000003</v>
-      </c>
-      <c r="F23" s="14">
-        <v>28</v>
-      </c>
-      <c r="G23" s="14">
-        <v>19</v>
-      </c>
-      <c r="H23" s="14">
-        <v>50.954000000000001</v>
-      </c>
-      <c r="I23" s="12">
-        <v>0</v>
-      </c>
-      <c r="J23" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K23" s="12">
-        <v>1</v>
-      </c>
-      <c r="L23" s="12" t="str">
-        <f>LOOKUP(J23,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M23" s="12">
-        <f>LOOKUP(J23,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N23" s="12">
-        <f>LOOKUP(J23,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O23" s="12">
-        <v>0</v>
-      </c>
+      <c r="A23" s="14"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C24" s="14">
-        <v>9</v>
-      </c>
-      <c r="D24" s="14">
-        <v>36</v>
-      </c>
-      <c r="E24" s="14">
-        <v>1.6372</v>
-      </c>
-      <c r="F24" s="14">
-        <v>-21</v>
-      </c>
-      <c r="G24" s="14">
-        <v>39</v>
-      </c>
-      <c r="H24" s="14">
-        <v>38.877000000000002</v>
-      </c>
-      <c r="I24" s="12">
-        <v>0</v>
-      </c>
-      <c r="J24" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K24" s="12">
-        <v>1</v>
-      </c>
-      <c r="L24" s="12" t="str">
-        <f>LOOKUP(J24,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M24" s="12">
-        <f>LOOKUP(J24,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N24" s="12">
-        <f>LOOKUP(J24,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O24" s="12">
-        <v>0</v>
-      </c>
+      <c r="A24" s="14"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C25" s="14">
-        <v>8</v>
-      </c>
-      <c r="D25" s="14">
-        <v>18</v>
-      </c>
-      <c r="E25" s="14">
-        <v>7.6214000000000004</v>
-      </c>
-      <c r="F25" s="14">
-        <v>-68</v>
-      </c>
-      <c r="G25" s="14">
-        <v>18</v>
-      </c>
-      <c r="H25" s="14">
-        <v>46.805</v>
-      </c>
-      <c r="I25" s="12">
-        <v>0</v>
-      </c>
-      <c r="J25" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K25" s="12">
-        <v>1</v>
-      </c>
-      <c r="L25" s="12" t="str">
-        <f>LOOKUP(J25,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M25" s="12">
-        <f>LOOKUP(J25,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N25" s="12">
-        <f>LOOKUP(J25,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O25" s="12">
-        <v>0</v>
-      </c>
+      <c r="A25" s="14"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="12"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" s="14">
-        <v>15</v>
-      </c>
-      <c r="D26" s="14">
-        <v>9</v>
-      </c>
-      <c r="E26" s="14">
-        <v>4.8933</v>
-      </c>
-      <c r="F26" s="14">
-        <v>-42</v>
-      </c>
-      <c r="G26" s="14">
-        <v>42</v>
-      </c>
-      <c r="H26" s="14">
-        <v>17.789000000000001</v>
-      </c>
-      <c r="I26" s="12">
-        <v>0</v>
-      </c>
-      <c r="J26" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K26" s="12">
-        <v>1</v>
-      </c>
-      <c r="L26" s="12" t="str">
-        <f>LOOKUP(J26,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M26" s="12">
-        <f>LOOKUP(J26,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N26" s="12">
-        <f>LOOKUP(J26,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O26" s="12">
-        <v>0</v>
-      </c>
+      <c r="A26" s="14"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" s="14">
-        <v>4</v>
-      </c>
-      <c r="D27" s="14">
-        <v>5</v>
-      </c>
-      <c r="E27" s="14">
-        <v>19.590900000000001</v>
-      </c>
-      <c r="F27" s="14">
-        <v>20</v>
-      </c>
-      <c r="G27" s="14">
-        <v>9</v>
-      </c>
-      <c r="H27" s="14">
-        <v>25.562999999999999</v>
-      </c>
-      <c r="I27" s="12">
-        <v>0</v>
-      </c>
-      <c r="J27" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K27" s="12">
-        <v>1</v>
-      </c>
-      <c r="L27" s="12" t="str">
-        <f>LOOKUP(J27,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M27" s="12">
-        <f>LOOKUP(J27,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N27" s="12">
-        <f>LOOKUP(J27,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O27" s="12">
-        <v>0</v>
-      </c>
+      <c r="A27" s="14"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="12"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C28" s="14">
-        <v>22</v>
-      </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="14">
-        <v>10.7727</v>
-      </c>
-      <c r="F28" s="14">
-        <v>18</v>
-      </c>
-      <c r="G28" s="14">
-        <v>53</v>
-      </c>
-      <c r="H28" s="14">
-        <v>3.5489999999999999</v>
-      </c>
-      <c r="I28" s="12">
-        <v>0</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K28" s="12">
-        <v>1</v>
-      </c>
-      <c r="L28" s="12" t="str">
-        <f>LOOKUP(J28,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M28" s="12">
-        <f>LOOKUP(J28,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N28" s="12">
-        <f>LOOKUP(J28,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O28" s="12">
-        <v>0</v>
-      </c>
+      <c r="A28" s="14"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C29" s="14">
-        <v>3</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="14">
-        <v>51.393599999999999</v>
-      </c>
-      <c r="F29" s="14">
-        <v>-16</v>
-      </c>
-      <c r="G29" s="14">
-        <v>35</v>
-      </c>
-      <c r="H29" s="14">
-        <v>36.030999999999999</v>
-      </c>
-      <c r="I29" s="12">
-        <v>0</v>
-      </c>
-      <c r="J29" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K29" s="12">
-        <v>1</v>
-      </c>
-      <c r="L29" s="12" t="str">
-        <f>LOOKUP(J29,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M29" s="12">
-        <f>LOOKUP(J29,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N29" s="12">
-        <f>LOOKUP(J29,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O29" s="12">
-        <v>0</v>
-      </c>
+      <c r="A29" s="14"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C30" s="14">
-        <v>12</v>
-      </c>
-      <c r="D30" s="14">
-        <v>47</v>
-      </c>
-      <c r="E30" s="14">
-        <v>56.624499999999998</v>
-      </c>
-      <c r="F30" s="14">
-        <v>9</v>
-      </c>
-      <c r="G30" s="14">
-        <v>45</v>
-      </c>
-      <c r="H30" s="14">
-        <v>5.0350000000000001</v>
-      </c>
-      <c r="I30" s="12">
-        <v>0</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K30" s="12">
-        <v>1</v>
-      </c>
-      <c r="L30" s="12" t="str">
-        <f>LOOKUP(J30,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M30" s="12">
-        <f>LOOKUP(J30,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N30" s="12">
-        <f>LOOKUP(J30,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O30" s="12">
-        <v>0</v>
-      </c>
+      <c r="A30" s="14"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" s="14">
-        <v>9</v>
-      </c>
-      <c r="D31" s="14">
-        <v>44</v>
-      </c>
-      <c r="E31" s="14">
-        <v>29.8367</v>
-      </c>
-      <c r="F31" s="14">
-        <v>-45</v>
-      </c>
-      <c r="G31" s="14">
-        <v>46</v>
-      </c>
-      <c r="H31" s="14">
-        <v>35.427</v>
-      </c>
-      <c r="I31" s="12">
-        <v>0</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K31" s="12">
-        <v>1</v>
-      </c>
-      <c r="L31" s="12" t="str">
-        <f>LOOKUP(J31,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M31" s="12">
-        <f>LOOKUP(J31,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N31" s="12">
-        <f>LOOKUP(J31,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O31" s="12">
-        <v>0</v>
-      </c>
+      <c r="A31" s="14"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C32" s="14">
-        <v>9</v>
-      </c>
-      <c r="D32" s="14">
-        <v>21</v>
-      </c>
-      <c r="E32" s="14">
-        <v>37.601500000000001</v>
-      </c>
-      <c r="F32" s="14">
-        <v>-60</v>
-      </c>
-      <c r="G32" s="14">
-        <v>16</v>
-      </c>
-      <c r="H32" s="14">
-        <v>55.03</v>
-      </c>
-      <c r="I32" s="12">
-        <v>0</v>
-      </c>
-      <c r="J32" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K32" s="12">
-        <v>1</v>
-      </c>
-      <c r="L32" s="12" t="str">
-        <f>LOOKUP(J32,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M32" s="12">
-        <f>LOOKUP(J32,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N32" s="12">
-        <f>LOOKUP(J32,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O32" s="12">
-        <v>0</v>
-      </c>
+      <c r="A32" s="14"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C33" s="14">
-        <v>19</v>
-      </c>
-      <c r="D33" s="14">
-        <v>20</v>
-      </c>
-      <c r="E33" s="14">
-        <v>54.376100000000001</v>
-      </c>
-      <c r="F33" s="14">
-        <v>-82</v>
-      </c>
-      <c r="G33" s="14">
-        <v>33</v>
-      </c>
-      <c r="H33" s="14">
-        <v>16.167000000000002</v>
-      </c>
-      <c r="I33" s="12">
-        <v>0</v>
-      </c>
-      <c r="J33" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K33" s="12">
-        <v>1</v>
-      </c>
-      <c r="L33" s="12" t="str">
-        <f>LOOKUP(J33,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M33" s="12">
-        <f>LOOKUP(J33,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N33" s="12">
-        <f>LOOKUP(J33,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O33" s="12">
-        <v>0</v>
-      </c>
+      <c r="A33" s="14"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="12"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C34" s="14">
-        <v>0</v>
-      </c>
-      <c r="D34" s="14">
-        <v>19</v>
-      </c>
-      <c r="E34" s="14">
-        <v>5.5622999999999996</v>
-      </c>
-      <c r="F34" s="14">
-        <v>-9</v>
-      </c>
-      <c r="G34" s="14">
-        <v>57</v>
-      </c>
-      <c r="H34" s="14">
-        <v>53.468000000000004</v>
-      </c>
-      <c r="I34" s="12">
-        <v>0</v>
-      </c>
-      <c r="J34" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K34" s="12">
-        <v>1</v>
-      </c>
-      <c r="L34" s="12" t="str">
-        <f>LOOKUP(J34,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M34" s="12">
-        <f>LOOKUP(J34,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N34" s="12">
-        <f>LOOKUP(J34,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O34" s="12">
-        <v>0</v>
-      </c>
+      <c r="A34" s="14"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="12"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C35" s="14">
-        <v>11</v>
-      </c>
-      <c r="D35" s="14">
-        <v>54</v>
-      </c>
-      <c r="E35" s="14">
-        <v>18.392099999999999</v>
-      </c>
-      <c r="F35" s="14">
-        <v>-37</v>
-      </c>
-      <c r="G35" s="14">
-        <v>33</v>
-      </c>
-      <c r="H35" s="14">
-        <v>9.8369999999999997</v>
-      </c>
-      <c r="I35" s="12">
-        <v>0</v>
-      </c>
-      <c r="J35" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K35" s="12">
-        <v>1</v>
-      </c>
-      <c r="L35" s="12" t="str">
-        <f>LOOKUP(J35,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M35" s="12">
-        <f>LOOKUP(J35,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N35" s="12">
-        <f>LOOKUP(J35,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O35" s="12">
-        <v>0</v>
-      </c>
+      <c r="A35" s="14"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+      <c r="O35" s="12"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C36" s="14">
-        <v>15</v>
-      </c>
-      <c r="D36" s="14">
-        <v>0</v>
-      </c>
-      <c r="E36" s="14">
-        <v>19.398299999999999</v>
-      </c>
-      <c r="F36" s="14">
-        <v>-24</v>
-      </c>
-      <c r="G36" s="14">
-        <v>27</v>
-      </c>
-      <c r="H36" s="14">
-        <v>14.693</v>
-      </c>
-      <c r="I36" s="12">
-        <v>0</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K36" s="12">
-        <v>-1</v>
-      </c>
-      <c r="L36" s="12" t="str">
-        <f>LOOKUP(J36,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M36" s="12">
-        <v>10000</v>
-      </c>
-      <c r="N36" s="12">
-        <f>LOOKUP(J36,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O36" s="12">
-        <v>0</v>
-      </c>
+      <c r="A36" s="14"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="12"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" s="14">
-        <v>2</v>
-      </c>
-      <c r="D37" s="14">
-        <v>27</v>
-      </c>
-      <c r="E37" s="14">
-        <v>28.3781</v>
-      </c>
-      <c r="F37" s="14">
-        <v>-27</v>
-      </c>
-      <c r="G37" s="14">
-        <v>38</v>
-      </c>
-      <c r="H37" s="14">
-        <v>6.7359999999999998</v>
-      </c>
-      <c r="I37" s="12">
-        <v>0</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K37" s="12">
-        <v>1</v>
-      </c>
-      <c r="L37" s="12" t="str">
-        <f>LOOKUP(J37,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M37" s="12">
-        <f>LOOKUP(J37,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N37" s="12">
-        <f>LOOKUP(J37,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O37" s="12">
-        <v>0</v>
-      </c>
+      <c r="A37" s="14"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
+      <c r="N37" s="12"/>
+      <c r="O37" s="12"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" s="14">
-        <v>9</v>
-      </c>
-      <c r="D38" s="14">
-        <v>22</v>
-      </c>
-      <c r="E38" s="14">
-        <v>37.576799999999999</v>
-      </c>
-      <c r="F38" s="14">
-        <v>50</v>
-      </c>
-      <c r="G38" s="14">
-        <v>36</v>
-      </c>
-      <c r="H38" s="14">
-        <v>13.435</v>
-      </c>
-      <c r="I38" s="12">
-        <v>0</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K38" s="12">
-        <v>1</v>
-      </c>
-      <c r="L38" s="12" t="str">
-        <f>LOOKUP(J38,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M38" s="12">
-        <f>LOOKUP(J38,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N38" s="12">
-        <f>LOOKUP(J38,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O38" s="12">
-        <v>0</v>
-      </c>
+      <c r="A38" s="14"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="12"/>
+      <c r="N38" s="12"/>
+      <c r="O38" s="12"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C39" s="14">
-        <v>5</v>
-      </c>
-      <c r="D39" s="14">
-        <v>27</v>
-      </c>
-      <c r="E39" s="14">
-        <v>24.825800000000001</v>
-      </c>
-      <c r="F39" s="14">
-        <v>-14</v>
-      </c>
-      <c r="G39" s="14">
-        <v>16</v>
-      </c>
-      <c r="H39" s="14">
-        <v>37.045999999999999</v>
-      </c>
-      <c r="I39" s="12">
-        <v>0</v>
-      </c>
-      <c r="J39" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K39" s="12">
-        <v>1</v>
-      </c>
-      <c r="L39" s="12" t="str">
-        <f>LOOKUP(J39,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M39" s="12">
-        <f>LOOKUP(J39,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N39" s="12">
-        <f>LOOKUP(J39,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O39" s="12">
-        <v>0</v>
-      </c>
+      <c r="A39" s="14"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="12"/>
+      <c r="M39" s="12"/>
+      <c r="N39" s="12"/>
+      <c r="O39" s="12"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C40" s="14">
-        <v>9</v>
-      </c>
-      <c r="D40" s="14">
-        <v>39</v>
-      </c>
-      <c r="E40" s="14">
-        <v>30.086099999999998</v>
-      </c>
-      <c r="F40" s="14">
-        <v>-20</v>
-      </c>
-      <c r="G40" s="14">
-        <v>58</v>
-      </c>
-      <c r="H40" s="14">
-        <v>56.881</v>
-      </c>
-      <c r="I40" s="12">
-        <v>0</v>
-      </c>
-      <c r="J40" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K40" s="12">
-        <v>1</v>
-      </c>
-      <c r="L40" s="12" t="str">
-        <f>LOOKUP(J40,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M40" s="12">
-        <f>LOOKUP(J40,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N40" s="12">
-        <f>LOOKUP(J40,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O40" s="12">
-        <v>0</v>
-      </c>
+      <c r="A40" s="14"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="12"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C41" s="14">
-        <v>7</v>
-      </c>
-      <c r="D41" s="14">
-        <v>10</v>
-      </c>
-      <c r="E41" s="14">
-        <v>24.060400000000001</v>
-      </c>
-      <c r="F41" s="14">
-        <v>-39</v>
-      </c>
-      <c r="G41" s="14">
-        <v>5</v>
-      </c>
-      <c r="H41" s="14">
-        <v>50.570999999999998</v>
-      </c>
-      <c r="I41" s="12">
-        <v>0</v>
-      </c>
-      <c r="J41" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K41" s="12">
-        <v>1</v>
-      </c>
-      <c r="L41" s="12" t="str">
-        <f>LOOKUP(J41,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M41" s="12">
-        <f>LOOKUP(J41,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N41" s="12">
-        <f>LOOKUP(J41,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O41" s="12">
-        <v>0</v>
-      </c>
+      <c r="A41" s="14"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="12"/>
+      <c r="L41" s="12"/>
+      <c r="M41" s="12"/>
+      <c r="N41" s="12"/>
+      <c r="O41" s="12"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C42" s="14">
-        <v>5</v>
-      </c>
-      <c r="D42" s="14">
-        <v>5</v>
-      </c>
-      <c r="E42" s="14">
-        <v>30.6</v>
-      </c>
-      <c r="F42" s="14">
-        <v>52</v>
-      </c>
-      <c r="G42" s="14">
-        <v>49</v>
-      </c>
-      <c r="H42" s="14">
-        <v>54</v>
-      </c>
-      <c r="I42" s="12">
-        <v>0</v>
-      </c>
-      <c r="J42" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K42" s="12">
-        <v>1</v>
-      </c>
-      <c r="L42" s="12" t="str">
-        <f>LOOKUP(J42,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M42" s="12">
-        <f>LOOKUP(J42,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N42" s="12">
-        <f>LOOKUP(J42,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O42" s="12">
-        <v>0</v>
-      </c>
+      <c r="A42" s="14"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="12"/>
+      <c r="M42" s="12"/>
+      <c r="N42" s="12"/>
+      <c r="O42" s="12"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C43" s="14">
-        <v>5</v>
-      </c>
-      <c r="D43" s="14">
-        <v>52</v>
-      </c>
-      <c r="E43" s="14">
-        <v>27.5</v>
-      </c>
-      <c r="F43" s="14">
-        <v>15</v>
-      </c>
-      <c r="G43" s="14">
-        <v>53</v>
-      </c>
-      <c r="H43" s="14">
-        <v>17</v>
-      </c>
-      <c r="I43" s="12">
-        <v>0</v>
-      </c>
-      <c r="J43" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K43" s="12">
-        <v>1</v>
-      </c>
-      <c r="L43" s="12" t="str">
-        <f>LOOKUP(J43,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M43" s="12">
-        <f>LOOKUP(J43,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N43" s="12">
-        <f>LOOKUP(J43,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O43" s="12">
-        <v>0</v>
-      </c>
+      <c r="A43" s="14"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+      <c r="M43" s="12"/>
+      <c r="N43" s="12"/>
+      <c r="O43" s="12"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C44" s="14">
-        <v>12</v>
-      </c>
-      <c r="D44" s="14">
-        <v>57</v>
-      </c>
-      <c r="E44" s="14">
-        <v>2.4</v>
-      </c>
-      <c r="F44" s="14">
-        <v>22</v>
-      </c>
-      <c r="G44" s="14">
-        <v>1</v>
-      </c>
-      <c r="H44" s="14">
-        <v>56</v>
-      </c>
-      <c r="I44" s="12">
-        <v>0</v>
-      </c>
-      <c r="J44" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K44" s="12">
-        <v>1</v>
-      </c>
-      <c r="L44" s="12" t="str">
-        <f>LOOKUP(J44,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M44" s="12">
-        <f>LOOKUP(J44,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N44" s="12">
-        <f>LOOKUP(J44,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O44" s="12">
-        <v>0</v>
-      </c>
+      <c r="A44" s="14"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="12"/>
+      <c r="M44" s="12"/>
+      <c r="N44" s="12"/>
+      <c r="O44" s="12"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C45" s="14">
-        <v>13</v>
-      </c>
-      <c r="D45" s="14">
-        <v>16</v>
-      </c>
-      <c r="E45" s="14">
-        <v>22</v>
-      </c>
-      <c r="F45" s="14">
-        <v>29</v>
-      </c>
-      <c r="G45" s="14">
-        <v>5</v>
-      </c>
-      <c r="H45" s="14">
-        <v>57</v>
-      </c>
-      <c r="I45" s="12">
-        <v>0</v>
-      </c>
-      <c r="J45" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K45" s="12">
-        <v>1</v>
-      </c>
-      <c r="L45" s="12" t="str">
-        <f>LOOKUP(J45,Survey_Info!A:A,Survey_Info!G:G)</f>
-        <v>TTAG</v>
-      </c>
-      <c r="M45" s="12">
-        <f>LOOKUP(J45,Survey_Info!A:A,Survey_Info!D:D)</f>
-        <v>10000</v>
-      </c>
-      <c r="N45" s="12">
-        <f>LOOKUP(J45,Survey_Info!A:A, Survey_Info!J:J)</f>
-        <v>1000</v>
-      </c>
-      <c r="O45" s="12">
-        <v>0</v>
-      </c>
+      <c r="A45" s="14"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="14"/>
+      <c r="K45" s="12"/>
+      <c r="L45" s="12"/>
+      <c r="M45" s="12"/>
+      <c r="N45" s="12"/>
+      <c r="O45" s="12"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="14"/>
@@ -4175,39 +3255,39 @@
   <sheetData>
     <row r="1" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="13">
         <v>20</v>
@@ -4227,10 +3307,10 @@
         <v>8000000</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="I2" s="13">
         <v>2</v>
@@ -4241,7 +3321,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B3" s="13">
         <v>15</v>
@@ -4260,10 +3340,10 @@
         <v>5000000</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="I3" s="13">
         <v>1</v>
@@ -4274,7 +3354,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="B4" s="13">
         <v>4</v>
@@ -4294,10 +3374,10 @@
         <v>80000</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="I4" s="13">
         <v>3</v>
@@ -4344,25 +3424,25 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -4414,21 +3494,21 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="18"/>
+        <v>65</v>
+      </c>
+      <c r="F1" s="32"/>
       <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -4436,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="17">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="C2" s="17">
         <v>2</v>
@@ -4464,25 +3544,25 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="B2" s="17">
         <v>40.015000000000001</v>
@@ -4500,7 +3580,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="B3" s="17">
         <v>40.10078</v>
@@ -4517,7 +3597,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="B4" s="17">
         <v>45.854579999999999</v>
@@ -4534,7 +3614,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="B5" s="17">
         <v>53.778799999999997</v>
@@ -4562,10 +3642,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="B1" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -5386,13 +4466,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="19" x14ac:dyDescent="0.25">
